--- a/data/raw/BVSP.xlsx
+++ b/data/raw/BVSP.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,5021 +468,5001 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45833</v>
+        <v>45845</v>
       </c>
       <c r="B2" t="n">
-        <v>135767</v>
+        <v>139490</v>
       </c>
       <c r="C2" t="n">
-        <v>137163</v>
+        <v>141342</v>
       </c>
       <c r="D2" t="n">
-        <v>135565</v>
+        <v>139295</v>
       </c>
       <c r="E2" t="n">
-        <v>137163</v>
+        <v>141265</v>
       </c>
       <c r="F2" t="n">
-        <v>7705700</v>
+        <v>6117300</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45834</v>
+        <v>45846</v>
       </c>
       <c r="B3" t="n">
-        <v>137114</v>
+        <v>139303</v>
       </c>
       <c r="C3" t="n">
-        <v>137353</v>
+        <v>139591</v>
       </c>
       <c r="D3" t="n">
-        <v>135756</v>
+        <v>138770</v>
       </c>
       <c r="E3" t="n">
-        <v>135767</v>
+        <v>139491</v>
       </c>
       <c r="F3" t="n">
-        <v>8023300</v>
+        <v>6750100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45835</v>
+        <v>45847</v>
       </c>
       <c r="B4" t="n">
-        <v>136866</v>
+        <v>137481</v>
       </c>
       <c r="C4" t="n">
-        <v>137209</v>
+        <v>139331</v>
       </c>
       <c r="D4" t="n">
-        <v>136469</v>
+        <v>137299</v>
       </c>
       <c r="E4" t="n">
-        <v>137113</v>
+        <v>139303</v>
       </c>
       <c r="F4" t="n">
-        <v>6244500</v>
+        <v>7584500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45838</v>
+        <v>45848</v>
       </c>
       <c r="B5" t="n">
-        <v>138855</v>
+        <v>136743</v>
       </c>
       <c r="C5" t="n">
-        <v>139103</v>
+        <v>137472</v>
       </c>
       <c r="D5" t="n">
-        <v>136430</v>
+        <v>136015</v>
       </c>
       <c r="E5" t="n">
-        <v>136865</v>
+        <v>137472</v>
       </c>
       <c r="F5" t="n">
-        <v>7680300</v>
+        <v>9566200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45839</v>
+        <v>45849</v>
       </c>
       <c r="B6" t="n">
-        <v>139549</v>
+        <v>136187</v>
       </c>
       <c r="C6" t="n">
-        <v>139695</v>
+        <v>136742</v>
       </c>
       <c r="D6" t="n">
-        <v>138855</v>
+        <v>135528</v>
       </c>
       <c r="E6" t="n">
-        <v>138855</v>
+        <v>136742</v>
       </c>
       <c r="F6" t="n">
-        <v>6345700</v>
+        <v>7401900</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45840</v>
+        <v>45852</v>
       </c>
       <c r="B7" t="n">
-        <v>139051</v>
+        <v>135299</v>
       </c>
       <c r="C7" t="n">
-        <v>140049</v>
+        <v>136187</v>
       </c>
       <c r="D7" t="n">
-        <v>138384</v>
+        <v>134840</v>
       </c>
       <c r="E7" t="n">
-        <v>139586</v>
+        <v>136187</v>
       </c>
       <c r="F7" t="n">
-        <v>8811900</v>
+        <v>7325600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45841</v>
+        <v>45853</v>
       </c>
       <c r="B8" t="n">
-        <v>140928</v>
+        <v>135250</v>
       </c>
       <c r="C8" t="n">
-        <v>141304</v>
+        <v>136022</v>
       </c>
       <c r="D8" t="n">
-        <v>139051</v>
+        <v>134380</v>
       </c>
       <c r="E8" t="n">
-        <v>139051</v>
+        <v>135298</v>
       </c>
       <c r="F8" t="n">
-        <v>6082200</v>
+        <v>6904200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45842</v>
+        <v>45854</v>
       </c>
       <c r="B9" t="n">
-        <v>141478</v>
+        <v>135511</v>
       </c>
       <c r="C9" t="n">
-        <v>141537</v>
+        <v>135641</v>
       </c>
       <c r="D9" t="n">
-        <v>140597</v>
+        <v>134265</v>
       </c>
       <c r="E9" t="n">
-        <v>140928</v>
+        <v>135250</v>
       </c>
       <c r="F9" t="n">
-        <v>2114300</v>
+        <v>7833200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45845</v>
+        <v>45855</v>
       </c>
       <c r="B10" t="n">
-        <v>139490</v>
+        <v>135565</v>
       </c>
       <c r="C10" t="n">
-        <v>141342</v>
+        <v>135793</v>
       </c>
       <c r="D10" t="n">
-        <v>139295</v>
+        <v>135016</v>
       </c>
       <c r="E10" t="n">
-        <v>141265</v>
+        <v>135515</v>
       </c>
       <c r="F10" t="n">
-        <v>6117300</v>
+        <v>6800000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45846</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="n">
-        <v>139303</v>
+        <v>133382</v>
       </c>
       <c r="C11" t="n">
-        <v>139591</v>
+        <v>135563</v>
       </c>
       <c r="D11" t="n">
-        <v>138770</v>
+        <v>133296</v>
       </c>
       <c r="E11" t="n">
-        <v>139491</v>
+        <v>135563</v>
       </c>
       <c r="F11" t="n">
-        <v>6750100</v>
+        <v>10071800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45847</v>
+        <v>45859</v>
       </c>
       <c r="B12" t="n">
-        <v>137481</v>
+        <v>134167</v>
       </c>
       <c r="C12" t="n">
-        <v>139331</v>
+        <v>134865</v>
       </c>
       <c r="D12" t="n">
-        <v>137299</v>
+        <v>133367</v>
       </c>
       <c r="E12" t="n">
-        <v>139303</v>
+        <v>133382</v>
       </c>
       <c r="F12" t="n">
-        <v>7584500</v>
+        <v>6726700</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45848</v>
+        <v>45860</v>
       </c>
       <c r="B13" t="n">
-        <v>136743</v>
+        <v>134036</v>
       </c>
       <c r="C13" t="n">
-        <v>137472</v>
+        <v>135300</v>
       </c>
       <c r="D13" t="n">
-        <v>136015</v>
+        <v>133986</v>
       </c>
       <c r="E13" t="n">
-        <v>137472</v>
+        <v>134180</v>
       </c>
       <c r="F13" t="n">
-        <v>9566200</v>
+        <v>7052100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45849</v>
+        <v>45861</v>
       </c>
       <c r="B14" t="n">
-        <v>136187</v>
+        <v>135368</v>
       </c>
       <c r="C14" t="n">
-        <v>136742</v>
+        <v>135782</v>
       </c>
       <c r="D14" t="n">
-        <v>135528</v>
+        <v>133676</v>
       </c>
       <c r="E14" t="n">
-        <v>136742</v>
+        <v>134036</v>
       </c>
       <c r="F14" t="n">
-        <v>7401900</v>
+        <v>6527600</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45852</v>
+        <v>45862</v>
       </c>
       <c r="B15" t="n">
-        <v>135299</v>
+        <v>133808</v>
       </c>
       <c r="C15" t="n">
-        <v>136187</v>
+        <v>135363</v>
       </c>
       <c r="D15" t="n">
-        <v>134840</v>
+        <v>133648</v>
       </c>
       <c r="E15" t="n">
-        <v>136187</v>
+        <v>135357</v>
       </c>
       <c r="F15" t="n">
-        <v>7325600</v>
+        <v>5976800</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45853</v>
+        <v>45863</v>
       </c>
       <c r="B16" t="n">
-        <v>135250</v>
+        <v>133524</v>
       </c>
       <c r="C16" t="n">
-        <v>136022</v>
+        <v>134204</v>
       </c>
       <c r="D16" t="n">
-        <v>134380</v>
+        <v>133285</v>
       </c>
       <c r="E16" t="n">
-        <v>135298</v>
+        <v>133820</v>
       </c>
       <c r="F16" t="n">
-        <v>6904200</v>
+        <v>5560900</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45854</v>
+        <v>45866</v>
       </c>
       <c r="B17" t="n">
-        <v>135511</v>
+        <v>132129</v>
       </c>
       <c r="C17" t="n">
-        <v>135641</v>
+        <v>133902</v>
       </c>
       <c r="D17" t="n">
-        <v>134265</v>
+        <v>131550</v>
       </c>
       <c r="E17" t="n">
-        <v>135250</v>
+        <v>133538</v>
       </c>
       <c r="F17" t="n">
-        <v>7833200</v>
+        <v>6625600</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45855</v>
+        <v>45867</v>
       </c>
       <c r="B18" t="n">
-        <v>135565</v>
+        <v>132726</v>
       </c>
       <c r="C18" t="n">
-        <v>135793</v>
+        <v>133346</v>
       </c>
       <c r="D18" t="n">
-        <v>135016</v>
+        <v>132130</v>
       </c>
       <c r="E18" t="n">
-        <v>135515</v>
+        <v>132130</v>
       </c>
       <c r="F18" t="n">
-        <v>6800000</v>
+        <v>6324800</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45856</v>
+        <v>45868</v>
       </c>
       <c r="B19" t="n">
-        <v>133382</v>
+        <v>133990</v>
       </c>
       <c r="C19" t="n">
-        <v>135563</v>
+        <v>134368</v>
       </c>
       <c r="D19" t="n">
-        <v>133296</v>
+        <v>131883</v>
       </c>
       <c r="E19" t="n">
-        <v>135563</v>
+        <v>132702</v>
       </c>
       <c r="F19" t="n">
-        <v>10071800</v>
+        <v>8655300</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45859</v>
+        <v>45869</v>
       </c>
       <c r="B20" t="n">
-        <v>134167</v>
+        <v>133071</v>
       </c>
       <c r="C20" t="n">
-        <v>134865</v>
+        <v>133987</v>
       </c>
       <c r="D20" t="n">
-        <v>133367</v>
+        <v>132096</v>
       </c>
       <c r="E20" t="n">
-        <v>133382</v>
+        <v>133987</v>
       </c>
       <c r="F20" t="n">
-        <v>6726700</v>
+        <v>9196800</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45860</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>134036</v>
+        <v>132437</v>
       </c>
       <c r="C21" t="n">
-        <v>135300</v>
+        <v>133237</v>
       </c>
       <c r="D21" t="n">
-        <v>133986</v>
+        <v>132140</v>
       </c>
       <c r="E21" t="n">
-        <v>134180</v>
+        <v>132920</v>
       </c>
       <c r="F21" t="n">
-        <v>7052100</v>
+        <v>8497100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45861</v>
+        <v>45873</v>
       </c>
       <c r="B22" t="n">
-        <v>135368</v>
+        <v>132971</v>
       </c>
       <c r="C22" t="n">
-        <v>135782</v>
+        <v>133929</v>
       </c>
       <c r="D22" t="n">
-        <v>133676</v>
+        <v>132440</v>
       </c>
       <c r="E22" t="n">
-        <v>134036</v>
+        <v>132440</v>
       </c>
       <c r="F22" t="n">
-        <v>6527600</v>
+        <v>6136600</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45862</v>
+        <v>45874</v>
       </c>
       <c r="B23" t="n">
-        <v>133808</v>
+        <v>133151</v>
       </c>
       <c r="C23" t="n">
-        <v>135363</v>
+        <v>134233</v>
       </c>
       <c r="D23" t="n">
-        <v>133648</v>
+        <v>132682</v>
       </c>
       <c r="E23" t="n">
-        <v>135357</v>
+        <v>132971</v>
       </c>
       <c r="F23" t="n">
-        <v>5976800</v>
+        <v>6606300</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45863</v>
+        <v>45875</v>
       </c>
       <c r="B24" t="n">
-        <v>133524</v>
+        <v>134538</v>
       </c>
       <c r="C24" t="n">
-        <v>134204</v>
+        <v>135241</v>
       </c>
       <c r="D24" t="n">
-        <v>133285</v>
+        <v>133169</v>
       </c>
       <c r="E24" t="n">
-        <v>133820</v>
+        <v>133169</v>
       </c>
       <c r="F24" t="n">
-        <v>5560900</v>
+        <v>8681700</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45866</v>
+        <v>45876</v>
       </c>
       <c r="B25" t="n">
-        <v>132129</v>
+        <v>136528</v>
       </c>
       <c r="C25" t="n">
-        <v>133902</v>
+        <v>137007</v>
       </c>
       <c r="D25" t="n">
-        <v>131550</v>
+        <v>134534</v>
       </c>
       <c r="E25" t="n">
-        <v>133538</v>
+        <v>134538</v>
       </c>
       <c r="F25" t="n">
-        <v>6625600</v>
+        <v>9501000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45867</v>
+        <v>45877</v>
       </c>
       <c r="B26" t="n">
-        <v>132726</v>
+        <v>135913</v>
       </c>
       <c r="C26" t="n">
-        <v>133346</v>
+        <v>136761</v>
       </c>
       <c r="D26" t="n">
-        <v>132130</v>
+        <v>135659</v>
       </c>
       <c r="E26" t="n">
-        <v>132130</v>
+        <v>136526</v>
       </c>
       <c r="F26" t="n">
-        <v>6324800</v>
+        <v>9890600</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45868</v>
+        <v>45880</v>
       </c>
       <c r="B27" t="n">
-        <v>133990</v>
+        <v>135623</v>
       </c>
       <c r="C27" t="n">
-        <v>134368</v>
+        <v>136307</v>
       </c>
       <c r="D27" t="n">
-        <v>131883</v>
+        <v>135496</v>
       </c>
       <c r="E27" t="n">
-        <v>132702</v>
+        <v>135913</v>
       </c>
       <c r="F27" t="n">
-        <v>8655300</v>
+        <v>6947300</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45869</v>
+        <v>45881</v>
       </c>
       <c r="B28" t="n">
-        <v>133071</v>
+        <v>137914</v>
       </c>
       <c r="C28" t="n">
-        <v>133987</v>
+        <v>138414</v>
       </c>
       <c r="D28" t="n">
-        <v>132096</v>
+        <v>135629</v>
       </c>
       <c r="E28" t="n">
-        <v>133987</v>
+        <v>135629</v>
       </c>
       <c r="F28" t="n">
-        <v>9196800</v>
+        <v>8342100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45870</v>
+        <v>45882</v>
       </c>
       <c r="B29" t="n">
-        <v>132437</v>
+        <v>136687</v>
       </c>
       <c r="C29" t="n">
-        <v>133237</v>
+        <v>137913</v>
       </c>
       <c r="D29" t="n">
-        <v>132140</v>
+        <v>136535</v>
       </c>
       <c r="E29" t="n">
-        <v>132920</v>
+        <v>137911</v>
       </c>
       <c r="F29" t="n">
-        <v>8497100</v>
+        <v>9398500</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="B30" t="n">
-        <v>132971</v>
+        <v>136356</v>
       </c>
       <c r="C30" t="n">
-        <v>133929</v>
+        <v>137437</v>
       </c>
       <c r="D30" t="n">
-        <v>132440</v>
+        <v>135588</v>
       </c>
       <c r="E30" t="n">
-        <v>132440</v>
+        <v>136681</v>
       </c>
       <c r="F30" t="n">
-        <v>6136600</v>
+        <v>9667800</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45874</v>
+        <v>45884</v>
       </c>
       <c r="B31" t="n">
-        <v>133151</v>
+        <v>136341</v>
       </c>
       <c r="C31" t="n">
-        <v>134233</v>
+        <v>136431</v>
       </c>
       <c r="D31" t="n">
-        <v>132682</v>
+        <v>135583</v>
       </c>
       <c r="E31" t="n">
-        <v>132971</v>
+        <v>136354</v>
       </c>
       <c r="F31" t="n">
-        <v>6606300</v>
+        <v>9291000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45875</v>
+        <v>45887</v>
       </c>
       <c r="B32" t="n">
-        <v>134538</v>
+        <v>137322</v>
       </c>
       <c r="C32" t="n">
-        <v>135241</v>
+        <v>137902</v>
       </c>
       <c r="D32" t="n">
-        <v>133169</v>
+        <v>136341</v>
       </c>
       <c r="E32" t="n">
-        <v>133169</v>
+        <v>136341</v>
       </c>
       <c r="F32" t="n">
-        <v>8681700</v>
+        <v>8089900</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45876</v>
+        <v>45888</v>
       </c>
       <c r="B33" t="n">
-        <v>136528</v>
+        <v>134432</v>
       </c>
       <c r="C33" t="n">
-        <v>137007</v>
+        <v>137321</v>
       </c>
       <c r="D33" t="n">
-        <v>134534</v>
+        <v>133997</v>
       </c>
       <c r="E33" t="n">
-        <v>134538</v>
+        <v>137321</v>
       </c>
       <c r="F33" t="n">
-        <v>9501000</v>
+        <v>8684100</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45877</v>
+        <v>45889</v>
       </c>
       <c r="B34" t="n">
-        <v>135913</v>
+        <v>134667</v>
       </c>
       <c r="C34" t="n">
-        <v>136761</v>
+        <v>134964</v>
       </c>
       <c r="D34" t="n">
-        <v>135659</v>
+        <v>134122</v>
       </c>
       <c r="E34" t="n">
-        <v>136526</v>
+        <v>134431</v>
       </c>
       <c r="F34" t="n">
-        <v>9890600</v>
+        <v>6845000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45880</v>
+        <v>45890</v>
       </c>
       <c r="B35" t="n">
-        <v>135623</v>
+        <v>134511</v>
       </c>
       <c r="C35" t="n">
-        <v>136307</v>
+        <v>134837</v>
       </c>
       <c r="D35" t="n">
-        <v>135496</v>
+        <v>133874</v>
       </c>
       <c r="E35" t="n">
-        <v>135913</v>
+        <v>134664</v>
       </c>
       <c r="F35" t="n">
-        <v>6947300</v>
+        <v>6516300</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45881</v>
+        <v>45891</v>
       </c>
       <c r="B36" t="n">
-        <v>137914</v>
+        <v>137968</v>
       </c>
       <c r="C36" t="n">
-        <v>138414</v>
+        <v>138072</v>
       </c>
       <c r="D36" t="n">
-        <v>135629</v>
+        <v>134512</v>
       </c>
       <c r="E36" t="n">
-        <v>135629</v>
+        <v>134512</v>
       </c>
       <c r="F36" t="n">
-        <v>8342100</v>
+        <v>9315600</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45882</v>
+        <v>45894</v>
       </c>
       <c r="B37" t="n">
-        <v>136687</v>
+        <v>138025</v>
       </c>
       <c r="C37" t="n">
-        <v>137913</v>
+        <v>138890</v>
       </c>
       <c r="D37" t="n">
-        <v>136535</v>
+        <v>137971</v>
       </c>
       <c r="E37" t="n">
-        <v>137911</v>
+        <v>137971</v>
       </c>
       <c r="F37" t="n">
-        <v>9398500</v>
+        <v>5991700</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45883</v>
+        <v>45895</v>
       </c>
       <c r="B38" t="n">
-        <v>136356</v>
+        <v>137771</v>
       </c>
       <c r="C38" t="n">
-        <v>137437</v>
+        <v>138037</v>
       </c>
       <c r="D38" t="n">
-        <v>135588</v>
+        <v>137059</v>
       </c>
       <c r="E38" t="n">
-        <v>136681</v>
+        <v>138026</v>
       </c>
       <c r="F38" t="n">
-        <v>9667800</v>
+        <v>8453400</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45884</v>
+        <v>45896</v>
       </c>
       <c r="B39" t="n">
-        <v>136341</v>
+        <v>139206</v>
       </c>
       <c r="C39" t="n">
-        <v>136431</v>
+        <v>139281</v>
       </c>
       <c r="D39" t="n">
-        <v>135583</v>
+        <v>137456</v>
       </c>
       <c r="E39" t="n">
-        <v>136354</v>
+        <v>137773</v>
       </c>
       <c r="F39" t="n">
-        <v>9291000</v>
+        <v>6609100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45887</v>
+        <v>45897</v>
       </c>
       <c r="B40" t="n">
-        <v>137322</v>
+        <v>141049</v>
       </c>
       <c r="C40" t="n">
-        <v>137902</v>
+        <v>142138</v>
       </c>
       <c r="D40" t="n">
-        <v>136341</v>
+        <v>139206</v>
       </c>
       <c r="E40" t="n">
-        <v>136341</v>
+        <v>139206</v>
       </c>
       <c r="F40" t="n">
-        <v>8089900</v>
+        <v>9294800</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45888</v>
+        <v>45898</v>
       </c>
       <c r="B41" t="n">
-        <v>134432</v>
+        <v>141422</v>
       </c>
       <c r="C41" t="n">
-        <v>137321</v>
+        <v>142379</v>
       </c>
       <c r="D41" t="n">
-        <v>133997</v>
+        <v>141000</v>
       </c>
       <c r="E41" t="n">
-        <v>137321</v>
+        <v>141049</v>
       </c>
       <c r="F41" t="n">
-        <v>8684100</v>
+        <v>9333200</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45889</v>
+        <v>45901</v>
       </c>
       <c r="B42" t="n">
-        <v>134667</v>
+        <v>141125</v>
       </c>
       <c r="C42" t="n">
-        <v>134964</v>
+        <v>141950</v>
       </c>
       <c r="D42" t="n">
-        <v>134122</v>
+        <v>140878</v>
       </c>
       <c r="E42" t="n">
-        <v>134431</v>
+        <v>141423</v>
       </c>
       <c r="F42" t="n">
-        <v>6845000</v>
+        <v>3388000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45890</v>
+        <v>45902</v>
       </c>
       <c r="B43" t="n">
-        <v>134511</v>
+        <v>140335</v>
       </c>
       <c r="C43" t="n">
-        <v>134837</v>
+        <v>141279</v>
       </c>
       <c r="D43" t="n">
-        <v>133874</v>
+        <v>139625</v>
       </c>
       <c r="E43" t="n">
-        <v>134664</v>
+        <v>141279</v>
       </c>
       <c r="F43" t="n">
-        <v>6516300</v>
+        <v>8785200</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45891</v>
+        <v>45903</v>
       </c>
       <c r="B44" t="n">
-        <v>137968</v>
+        <v>139864</v>
       </c>
       <c r="C44" t="n">
-        <v>138072</v>
+        <v>140496</v>
       </c>
       <c r="D44" t="n">
-        <v>134512</v>
+        <v>139582</v>
       </c>
       <c r="E44" t="n">
-        <v>134512</v>
+        <v>140332</v>
       </c>
       <c r="F44" t="n">
-        <v>9315600</v>
+        <v>7579800</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45894</v>
+        <v>45904</v>
       </c>
       <c r="B45" t="n">
-        <v>138025</v>
+        <v>140993</v>
       </c>
       <c r="C45" t="n">
-        <v>138890</v>
+        <v>141482</v>
       </c>
       <c r="D45" t="n">
-        <v>137971</v>
+        <v>139832</v>
       </c>
       <c r="E45" t="n">
-        <v>137971</v>
+        <v>139832</v>
       </c>
       <c r="F45" t="n">
-        <v>5991700</v>
+        <v>8032400</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45895</v>
+        <v>45905</v>
       </c>
       <c r="B46" t="n">
-        <v>137771</v>
+        <v>142640</v>
       </c>
       <c r="C46" t="n">
-        <v>138037</v>
+        <v>143409</v>
       </c>
       <c r="D46" t="n">
-        <v>137059</v>
+        <v>141004</v>
       </c>
       <c r="E46" t="n">
-        <v>138026</v>
+        <v>141004</v>
       </c>
       <c r="F46" t="n">
-        <v>8453400</v>
+        <v>8379400</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45896</v>
+        <v>45908</v>
       </c>
       <c r="B47" t="n">
-        <v>139206</v>
+        <v>141792</v>
       </c>
       <c r="C47" t="n">
-        <v>139281</v>
+        <v>143089</v>
       </c>
       <c r="D47" t="n">
-        <v>137456</v>
+        <v>141329</v>
       </c>
       <c r="E47" t="n">
-        <v>137773</v>
+        <v>142640</v>
       </c>
       <c r="F47" t="n">
-        <v>6609100</v>
+        <v>7440900</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45897</v>
+        <v>45909</v>
       </c>
       <c r="B48" t="n">
-        <v>141049</v>
+        <v>141618</v>
       </c>
       <c r="C48" t="n">
-        <v>142138</v>
+        <v>142286</v>
       </c>
       <c r="D48" t="n">
-        <v>139206</v>
+        <v>141606</v>
       </c>
       <c r="E48" t="n">
-        <v>139206</v>
+        <v>141794</v>
       </c>
       <c r="F48" t="n">
-        <v>9294800</v>
+        <v>7481900</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45898</v>
+        <v>45910</v>
       </c>
       <c r="B49" t="n">
-        <v>141422</v>
+        <v>142349</v>
       </c>
       <c r="C49" t="n">
-        <v>142379</v>
+        <v>143182</v>
       </c>
       <c r="D49" t="n">
-        <v>141000</v>
+        <v>141612</v>
       </c>
       <c r="E49" t="n">
-        <v>141049</v>
+        <v>141612</v>
       </c>
       <c r="F49" t="n">
-        <v>9333200</v>
+        <v>7138700</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45901</v>
+        <v>45911</v>
       </c>
       <c r="B50" t="n">
-        <v>141125</v>
+        <v>143151</v>
       </c>
       <c r="C50" t="n">
-        <v>141950</v>
+        <v>144013</v>
       </c>
       <c r="D50" t="n">
-        <v>140878</v>
+        <v>142349</v>
       </c>
       <c r="E50" t="n">
-        <v>141423</v>
+        <v>142349</v>
       </c>
       <c r="F50" t="n">
-        <v>3388000</v>
+        <v>7570400</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="B51" t="n">
-        <v>140335</v>
+        <v>142272</v>
       </c>
       <c r="C51" t="n">
-        <v>141279</v>
+        <v>143202</v>
       </c>
       <c r="D51" t="n">
-        <v>139625</v>
+        <v>142241</v>
       </c>
       <c r="E51" t="n">
-        <v>141279</v>
+        <v>143151</v>
       </c>
       <c r="F51" t="n">
-        <v>8785200</v>
+        <v>6388600</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45903</v>
+        <v>45915</v>
       </c>
       <c r="B52" t="n">
-        <v>139864</v>
+        <v>143547</v>
       </c>
       <c r="C52" t="n">
-        <v>140496</v>
+        <v>144194</v>
       </c>
       <c r="D52" t="n">
-        <v>139582</v>
+        <v>142292</v>
       </c>
       <c r="E52" t="n">
-        <v>140332</v>
+        <v>142292</v>
       </c>
       <c r="F52" t="n">
-        <v>7579800</v>
+        <v>6614000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45904</v>
+        <v>45916</v>
       </c>
       <c r="B53" t="n">
-        <v>140993</v>
+        <v>144062</v>
       </c>
       <c r="C53" t="n">
-        <v>141482</v>
+        <v>144584</v>
       </c>
       <c r="D53" t="n">
-        <v>139832</v>
+        <v>143547</v>
       </c>
       <c r="E53" t="n">
-        <v>139832</v>
+        <v>143547</v>
       </c>
       <c r="F53" t="n">
-        <v>8032400</v>
+        <v>8478200</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45905</v>
+        <v>45917</v>
       </c>
       <c r="B54" t="n">
-        <v>142640</v>
+        <v>145594</v>
       </c>
       <c r="C54" t="n">
-        <v>143409</v>
+        <v>146331</v>
       </c>
       <c r="D54" t="n">
-        <v>141004</v>
+        <v>143910</v>
       </c>
       <c r="E54" t="n">
-        <v>141004</v>
+        <v>144059</v>
       </c>
       <c r="F54" t="n">
-        <v>8379400</v>
+        <v>9604400</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="B55" t="n">
-        <v>141792</v>
+        <v>145500</v>
       </c>
       <c r="C55" t="n">
-        <v>143089</v>
+        <v>145726</v>
       </c>
       <c r="D55" t="n">
-        <v>141329</v>
+        <v>144993</v>
       </c>
       <c r="E55" t="n">
-        <v>142640</v>
+        <v>145594</v>
       </c>
       <c r="F55" t="n">
-        <v>7440900</v>
+        <v>8372000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45909</v>
+        <v>45919</v>
       </c>
       <c r="B56" t="n">
-        <v>141618</v>
+        <v>145865</v>
       </c>
       <c r="C56" t="n">
-        <v>142286</v>
+        <v>146399</v>
       </c>
       <c r="D56" t="n">
-        <v>141606</v>
+        <v>145496</v>
       </c>
       <c r="E56" t="n">
-        <v>141794</v>
+        <v>145500</v>
       </c>
       <c r="F56" t="n">
-        <v>7481900</v>
+        <v>10279800</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45910</v>
+        <v>45922</v>
       </c>
       <c r="B57" t="n">
-        <v>142349</v>
+        <v>145109</v>
       </c>
       <c r="C57" t="n">
-        <v>143182</v>
+        <v>145864</v>
       </c>
       <c r="D57" t="n">
-        <v>141612</v>
+        <v>144117</v>
       </c>
       <c r="E57" t="n">
-        <v>141612</v>
+        <v>145864</v>
       </c>
       <c r="F57" t="n">
-        <v>7138700</v>
+        <v>9428100</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45911</v>
+        <v>45923</v>
       </c>
       <c r="B58" t="n">
-        <v>143151</v>
+        <v>146425</v>
       </c>
       <c r="C58" t="n">
-        <v>144013</v>
+        <v>147179</v>
       </c>
       <c r="D58" t="n">
-        <v>142349</v>
+        <v>145107</v>
       </c>
       <c r="E58" t="n">
-        <v>142349</v>
+        <v>145112</v>
       </c>
       <c r="F58" t="n">
-        <v>7570400</v>
+        <v>8143800</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45912</v>
+        <v>45924</v>
       </c>
       <c r="B59" t="n">
-        <v>142272</v>
+        <v>146492</v>
       </c>
       <c r="C59" t="n">
-        <v>143202</v>
+        <v>146585</v>
       </c>
       <c r="D59" t="n">
-        <v>142241</v>
+        <v>146067</v>
       </c>
       <c r="E59" t="n">
-        <v>143151</v>
+        <v>146426</v>
       </c>
       <c r="F59" t="n">
-        <v>6388600</v>
+        <v>7292900</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45915</v>
+        <v>45925</v>
       </c>
       <c r="B60" t="n">
-        <v>143547</v>
+        <v>145306</v>
       </c>
       <c r="C60" t="n">
-        <v>144194</v>
+        <v>146519</v>
       </c>
       <c r="D60" t="n">
-        <v>142292</v>
+        <v>145187</v>
       </c>
       <c r="E60" t="n">
-        <v>142292</v>
+        <v>146492</v>
       </c>
       <c r="F60" t="n">
-        <v>6614000</v>
+        <v>8293800</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45916</v>
+        <v>45926</v>
       </c>
       <c r="B61" t="n">
-        <v>144062</v>
+        <v>145447</v>
       </c>
       <c r="C61" t="n">
-        <v>144584</v>
+        <v>146235</v>
       </c>
       <c r="D61" t="n">
-        <v>143547</v>
+        <v>145146</v>
       </c>
       <c r="E61" t="n">
-        <v>143547</v>
+        <v>145326</v>
       </c>
       <c r="F61" t="n">
-        <v>8478200</v>
+        <v>6338200</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45917</v>
+        <v>45929</v>
       </c>
       <c r="B62" t="n">
-        <v>145594</v>
+        <v>146337</v>
       </c>
       <c r="C62" t="n">
-        <v>146331</v>
+        <v>147558</v>
       </c>
       <c r="D62" t="n">
-        <v>143910</v>
+        <v>145447</v>
       </c>
       <c r="E62" t="n">
-        <v>144059</v>
+        <v>145447</v>
       </c>
       <c r="F62" t="n">
-        <v>9604400</v>
+        <v>7074100</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45918</v>
+        <v>45930</v>
       </c>
       <c r="B63" t="n">
-        <v>145500</v>
+        <v>146237</v>
       </c>
       <c r="C63" t="n">
-        <v>145726</v>
+        <v>147578</v>
       </c>
       <c r="D63" t="n">
-        <v>144993</v>
+        <v>145774</v>
       </c>
       <c r="E63" t="n">
-        <v>145594</v>
+        <v>146337</v>
       </c>
       <c r="F63" t="n">
-        <v>8372000</v>
+        <v>9477300</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45919</v>
+        <v>45931</v>
       </c>
       <c r="B64" t="n">
-        <v>145865</v>
+        <v>145517</v>
       </c>
       <c r="C64" t="n">
-        <v>146399</v>
+        <v>146879</v>
       </c>
       <c r="D64" t="n">
-        <v>145496</v>
+        <v>145193</v>
       </c>
       <c r="E64" t="n">
-        <v>145500</v>
+        <v>146237</v>
       </c>
       <c r="F64" t="n">
-        <v>10279800</v>
+        <v>8340700</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45922</v>
+        <v>45932</v>
       </c>
       <c r="B65" t="n">
-        <v>145109</v>
+        <v>143950</v>
       </c>
       <c r="C65" t="n">
-        <v>145864</v>
+        <v>145621</v>
       </c>
       <c r="D65" t="n">
-        <v>144117</v>
+        <v>143635</v>
       </c>
       <c r="E65" t="n">
-        <v>145864</v>
+        <v>145517</v>
       </c>
       <c r="F65" t="n">
-        <v>9428100</v>
+        <v>7245600</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45923</v>
+        <v>45933</v>
       </c>
       <c r="B66" t="n">
-        <v>146425</v>
+        <v>144201</v>
       </c>
       <c r="C66" t="n">
-        <v>147179</v>
+        <v>144518</v>
       </c>
       <c r="D66" t="n">
-        <v>145107</v>
+        <v>143676</v>
       </c>
       <c r="E66" t="n">
-        <v>145112</v>
+        <v>143950</v>
       </c>
       <c r="F66" t="n">
-        <v>8143800</v>
+        <v>6177600</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45924</v>
+        <v>45936</v>
       </c>
       <c r="B67" t="n">
-        <v>146492</v>
+        <v>143608</v>
       </c>
       <c r="C67" t="n">
-        <v>146585</v>
+        <v>144532</v>
       </c>
       <c r="D67" t="n">
-        <v>146067</v>
+        <v>143376</v>
       </c>
       <c r="E67" t="n">
-        <v>146426</v>
+        <v>144202</v>
       </c>
       <c r="F67" t="n">
-        <v>7292900</v>
+        <v>5981500</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45925</v>
+        <v>45937</v>
       </c>
       <c r="B68" t="n">
-        <v>145306</v>
+        <v>141356</v>
       </c>
       <c r="C68" t="n">
-        <v>146519</v>
+        <v>143606</v>
       </c>
       <c r="D68" t="n">
-        <v>145187</v>
+        <v>141035</v>
       </c>
       <c r="E68" t="n">
-        <v>146492</v>
+        <v>143606</v>
       </c>
       <c r="F68" t="n">
-        <v>8293800</v>
+        <v>9272700</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45926</v>
+        <v>45938</v>
       </c>
       <c r="B69" t="n">
-        <v>145447</v>
+        <v>142145</v>
       </c>
       <c r="C69" t="n">
-        <v>146235</v>
+        <v>142385</v>
       </c>
       <c r="D69" t="n">
-        <v>145146</v>
+        <v>141356</v>
       </c>
       <c r="E69" t="n">
-        <v>145326</v>
+        <v>141356</v>
       </c>
       <c r="F69" t="n">
-        <v>6338200</v>
+        <v>7525200</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45929</v>
+        <v>45939</v>
       </c>
       <c r="B70" t="n">
-        <v>146337</v>
+        <v>141708</v>
       </c>
       <c r="C70" t="n">
-        <v>147558</v>
+        <v>143212</v>
       </c>
       <c r="D70" t="n">
-        <v>145447</v>
+        <v>141603</v>
       </c>
       <c r="E70" t="n">
-        <v>145447</v>
+        <v>142148</v>
       </c>
       <c r="F70" t="n">
-        <v>7074100</v>
+        <v>6821400</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="B71" t="n">
-        <v>146237</v>
+        <v>140680</v>
       </c>
       <c r="C71" t="n">
-        <v>147578</v>
+        <v>142274</v>
       </c>
       <c r="D71" t="n">
-        <v>145774</v>
+        <v>140231</v>
       </c>
       <c r="E71" t="n">
-        <v>146337</v>
+        <v>141725</v>
       </c>
       <c r="F71" t="n">
-        <v>9477300</v>
+        <v>8280800</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45931</v>
+        <v>45943</v>
       </c>
       <c r="B72" t="n">
-        <v>145517</v>
+        <v>141783</v>
       </c>
       <c r="C72" t="n">
-        <v>146879</v>
+        <v>142303</v>
       </c>
       <c r="D72" t="n">
-        <v>145193</v>
+        <v>140682</v>
       </c>
       <c r="E72" t="n">
-        <v>146237</v>
+        <v>140682</v>
       </c>
       <c r="F72" t="n">
-        <v>8340700</v>
+        <v>5531200</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45932</v>
+        <v>45944</v>
       </c>
       <c r="B73" t="n">
-        <v>143950</v>
+        <v>141683</v>
       </c>
       <c r="C73" t="n">
-        <v>145621</v>
+        <v>142589</v>
       </c>
       <c r="D73" t="n">
-        <v>143635</v>
+        <v>141334</v>
       </c>
       <c r="E73" t="n">
-        <v>145517</v>
+        <v>141788</v>
       </c>
       <c r="F73" t="n">
-        <v>7245600</v>
+        <v>7122300</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45933</v>
+        <v>45945</v>
       </c>
       <c r="B74" t="n">
-        <v>144201</v>
+        <v>142604</v>
       </c>
       <c r="C74" t="n">
-        <v>144518</v>
+        <v>142905</v>
       </c>
       <c r="D74" t="n">
-        <v>143676</v>
+        <v>141154</v>
       </c>
       <c r="E74" t="n">
-        <v>143950</v>
+        <v>141683</v>
       </c>
       <c r="F74" t="n">
-        <v>6177600</v>
+        <v>10321000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45936</v>
+        <v>45946</v>
       </c>
       <c r="B75" t="n">
-        <v>143608</v>
+        <v>142200</v>
       </c>
       <c r="C75" t="n">
-        <v>144532</v>
+        <v>143191</v>
       </c>
       <c r="D75" t="n">
-        <v>143376</v>
+        <v>141446</v>
       </c>
       <c r="E75" t="n">
-        <v>144202</v>
+        <v>142604</v>
       </c>
       <c r="F75" t="n">
-        <v>5981500</v>
+        <v>7391900</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45937</v>
+        <v>45947</v>
       </c>
       <c r="B76" t="n">
-        <v>141356</v>
+        <v>143399</v>
       </c>
       <c r="C76" t="n">
-        <v>143606</v>
+        <v>143425</v>
       </c>
       <c r="D76" t="n">
-        <v>141035</v>
+        <v>141248</v>
       </c>
       <c r="E76" t="n">
-        <v>143606</v>
+        <v>142200</v>
       </c>
       <c r="F76" t="n">
-        <v>9272700</v>
+        <v>8875100</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45938</v>
+        <v>45950</v>
       </c>
       <c r="B77" t="n">
-        <v>142145</v>
+        <v>144509</v>
       </c>
       <c r="C77" t="n">
-        <v>142385</v>
+        <v>145216</v>
       </c>
       <c r="D77" t="n">
-        <v>141356</v>
+        <v>143396</v>
       </c>
       <c r="E77" t="n">
-        <v>141356</v>
+        <v>143399</v>
       </c>
       <c r="F77" t="n">
-        <v>7525200</v>
+        <v>6793400</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45939</v>
+        <v>45951</v>
       </c>
       <c r="B78" t="n">
-        <v>141708</v>
+        <v>144085</v>
       </c>
       <c r="C78" t="n">
-        <v>143212</v>
+        <v>144795</v>
       </c>
       <c r="D78" t="n">
-        <v>141603</v>
+        <v>143829</v>
       </c>
       <c r="E78" t="n">
-        <v>142148</v>
+        <v>144509</v>
       </c>
       <c r="F78" t="n">
-        <v>6821400</v>
+        <v>6193200</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45940</v>
+        <v>45952</v>
       </c>
       <c r="B79" t="n">
-        <v>140680</v>
+        <v>144873</v>
       </c>
       <c r="C79" t="n">
-        <v>142274</v>
+        <v>145048</v>
       </c>
       <c r="D79" t="n">
-        <v>140231</v>
+        <v>144039</v>
       </c>
       <c r="E79" t="n">
-        <v>141725</v>
+        <v>144094</v>
       </c>
       <c r="F79" t="n">
-        <v>8280800</v>
+        <v>7025000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45943</v>
+        <v>45953</v>
       </c>
       <c r="B80" t="n">
-        <v>141783</v>
+        <v>145721</v>
       </c>
       <c r="C80" t="n">
-        <v>142303</v>
+        <v>146358</v>
       </c>
       <c r="D80" t="n">
-        <v>140682</v>
+        <v>144881</v>
       </c>
       <c r="E80" t="n">
-        <v>140682</v>
+        <v>144881</v>
       </c>
       <c r="F80" t="n">
-        <v>5531200</v>
+        <v>6599600</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45944</v>
+        <v>45954</v>
       </c>
       <c r="B81" t="n">
-        <v>141683</v>
+        <v>146172</v>
       </c>
       <c r="C81" t="n">
-        <v>142589</v>
+        <v>147240</v>
       </c>
       <c r="D81" t="n">
-        <v>141334</v>
+        <v>145721</v>
       </c>
       <c r="E81" t="n">
-        <v>141788</v>
+        <v>145721</v>
       </c>
       <c r="F81" t="n">
-        <v>7122300</v>
+        <v>6491300</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45945</v>
+        <v>45957</v>
       </c>
       <c r="B82" t="n">
-        <v>142604</v>
+        <v>146969</v>
       </c>
       <c r="C82" t="n">
-        <v>142905</v>
+        <v>147977</v>
       </c>
       <c r="D82" t="n">
-        <v>141154</v>
+        <v>146174</v>
       </c>
       <c r="E82" t="n">
-        <v>141683</v>
+        <v>146174</v>
       </c>
       <c r="F82" t="n">
-        <v>10321000</v>
+        <v>6445200</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45946</v>
+        <v>45958</v>
       </c>
       <c r="B83" t="n">
-        <v>142200</v>
+        <v>147429</v>
       </c>
       <c r="C83" t="n">
-        <v>143191</v>
+        <v>147811</v>
       </c>
       <c r="D83" t="n">
-        <v>141446</v>
+        <v>146575</v>
       </c>
       <c r="E83" t="n">
-        <v>142604</v>
+        <v>146970</v>
       </c>
       <c r="F83" t="n">
-        <v>7391900</v>
+        <v>7108000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45947</v>
+        <v>45959</v>
       </c>
       <c r="B84" t="n">
-        <v>143399</v>
+        <v>148633</v>
       </c>
       <c r="C84" t="n">
-        <v>143425</v>
+        <v>149067</v>
       </c>
       <c r="D84" t="n">
-        <v>141248</v>
+        <v>147430</v>
       </c>
       <c r="E84" t="n">
-        <v>142200</v>
+        <v>147430</v>
       </c>
       <c r="F84" t="n">
-        <v>8875100</v>
+        <v>7999500</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45950</v>
+        <v>45960</v>
       </c>
       <c r="B85" t="n">
-        <v>144509</v>
+        <v>148780</v>
       </c>
       <c r="C85" t="n">
-        <v>145216</v>
+        <v>149234</v>
       </c>
       <c r="D85" t="n">
-        <v>143396</v>
+        <v>147547</v>
       </c>
       <c r="E85" t="n">
-        <v>143399</v>
+        <v>148632</v>
       </c>
       <c r="F85" t="n">
-        <v>6793400</v>
+        <v>7300600</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45951</v>
+        <v>45961</v>
       </c>
       <c r="B86" t="n">
-        <v>144085</v>
+        <v>149540</v>
       </c>
       <c r="C86" t="n">
-        <v>144795</v>
+        <v>149636</v>
       </c>
       <c r="D86" t="n">
-        <v>143829</v>
+        <v>148774</v>
       </c>
       <c r="E86" t="n">
-        <v>144509</v>
+        <v>148774</v>
       </c>
       <c r="F86" t="n">
-        <v>6193200</v>
+        <v>8911000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45952</v>
+        <v>45964</v>
       </c>
       <c r="B87" t="n">
-        <v>144873</v>
+        <v>150454</v>
       </c>
       <c r="C87" t="n">
-        <v>145048</v>
+        <v>150761</v>
       </c>
       <c r="D87" t="n">
-        <v>144039</v>
+        <v>149551</v>
       </c>
       <c r="E87" t="n">
-        <v>144094</v>
+        <v>149551</v>
       </c>
       <c r="F87" t="n">
-        <v>7025000</v>
+        <v>7667600</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45953</v>
+        <v>45965</v>
       </c>
       <c r="B88" t="n">
-        <v>145721</v>
+        <v>150704</v>
       </c>
       <c r="C88" t="n">
-        <v>146358</v>
+        <v>150888</v>
       </c>
       <c r="D88" t="n">
-        <v>144881</v>
+        <v>149979</v>
       </c>
       <c r="E88" t="n">
-        <v>144881</v>
+        <v>150454</v>
       </c>
       <c r="F88" t="n">
-        <v>6599600</v>
+        <v>7541200</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45954</v>
+        <v>45966</v>
       </c>
       <c r="B89" t="n">
-        <v>146172</v>
+        <v>153294</v>
       </c>
       <c r="C89" t="n">
-        <v>147240</v>
+        <v>153583</v>
       </c>
       <c r="D89" t="n">
-        <v>145721</v>
+        <v>150296</v>
       </c>
       <c r="E89" t="n">
-        <v>145721</v>
+        <v>150709</v>
       </c>
       <c r="F89" t="n">
-        <v>6491300</v>
+        <v>9803000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45957</v>
+        <v>45967</v>
       </c>
       <c r="B90" t="n">
-        <v>146969</v>
+        <v>153339</v>
       </c>
       <c r="C90" t="n">
-        <v>147977</v>
+        <v>154352</v>
       </c>
       <c r="D90" t="n">
-        <v>146174</v>
+        <v>153235</v>
       </c>
       <c r="E90" t="n">
-        <v>146174</v>
+        <v>153297</v>
       </c>
       <c r="F90" t="n">
-        <v>6445200</v>
+        <v>9387600</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45958</v>
+        <v>45968</v>
       </c>
       <c r="B91" t="n">
-        <v>147429</v>
+        <v>154064</v>
       </c>
       <c r="C91" t="n">
-        <v>147811</v>
+        <v>154066</v>
       </c>
       <c r="D91" t="n">
-        <v>146575</v>
+        <v>152368</v>
       </c>
       <c r="E91" t="n">
-        <v>146970</v>
+        <v>153339</v>
       </c>
       <c r="F91" t="n">
-        <v>7108000</v>
+        <v>9474100</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45959</v>
+        <v>45971</v>
       </c>
       <c r="B92" t="n">
-        <v>148633</v>
+        <v>155257</v>
       </c>
       <c r="C92" t="n">
-        <v>149067</v>
+        <v>155601</v>
       </c>
       <c r="D92" t="n">
-        <v>147430</v>
+        <v>154058</v>
       </c>
       <c r="E92" t="n">
-        <v>147430</v>
+        <v>154061</v>
       </c>
       <c r="F92" t="n">
-        <v>7999500</v>
+        <v>7751600</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45960</v>
+        <v>45972</v>
       </c>
       <c r="B93" t="n">
-        <v>148780</v>
+        <v>157749</v>
       </c>
       <c r="C93" t="n">
-        <v>149234</v>
+        <v>158467</v>
       </c>
       <c r="D93" t="n">
-        <v>147547</v>
+        <v>155252</v>
       </c>
       <c r="E93" t="n">
-        <v>148632</v>
+        <v>155257</v>
       </c>
       <c r="F93" t="n">
-        <v>7300600</v>
+        <v>12876000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45961</v>
+        <v>45973</v>
       </c>
       <c r="B94" t="n">
-        <v>149540</v>
+        <v>157633</v>
       </c>
       <c r="C94" t="n">
-        <v>149636</v>
+        <v>158134</v>
       </c>
       <c r="D94" t="n">
-        <v>148774</v>
+        <v>156560</v>
       </c>
       <c r="E94" t="n">
-        <v>148774</v>
+        <v>157749</v>
       </c>
       <c r="F94" t="n">
-        <v>8911000</v>
+        <v>11226600</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45964</v>
+        <v>45974</v>
       </c>
       <c r="B95" t="n">
-        <v>150454</v>
+        <v>157162</v>
       </c>
       <c r="C95" t="n">
-        <v>150761</v>
+        <v>158319</v>
       </c>
       <c r="D95" t="n">
-        <v>149551</v>
+        <v>156509</v>
       </c>
       <c r="E95" t="n">
-        <v>149551</v>
+        <v>157633</v>
       </c>
       <c r="F95" t="n">
-        <v>7667600</v>
+        <v>10560800</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45965</v>
+        <v>45975</v>
       </c>
       <c r="B96" t="n">
-        <v>150704</v>
+        <v>157739</v>
       </c>
       <c r="C96" t="n">
-        <v>150888</v>
+        <v>158366</v>
       </c>
       <c r="D96" t="n">
-        <v>149979</v>
+        <v>156656</v>
       </c>
       <c r="E96" t="n">
-        <v>150454</v>
+        <v>157162</v>
       </c>
       <c r="F96" t="n">
-        <v>7541200</v>
+        <v>7977300</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45966</v>
+        <v>45978</v>
       </c>
       <c r="B97" t="n">
-        <v>153294</v>
+        <v>156993</v>
       </c>
       <c r="C97" t="n">
-        <v>153583</v>
+        <v>157901</v>
       </c>
       <c r="D97" t="n">
-        <v>150296</v>
+        <v>156568</v>
       </c>
       <c r="E97" t="n">
-        <v>150709</v>
+        <v>157742</v>
       </c>
       <c r="F97" t="n">
-        <v>9803000</v>
+        <v>8419200</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45967</v>
+        <v>45979</v>
       </c>
       <c r="B98" t="n">
-        <v>153339</v>
+        <v>156522</v>
       </c>
       <c r="C98" t="n">
-        <v>154352</v>
+        <v>157040</v>
       </c>
       <c r="D98" t="n">
-        <v>153235</v>
+        <v>155834</v>
       </c>
       <c r="E98" t="n">
-        <v>153297</v>
+        <v>156990</v>
       </c>
       <c r="F98" t="n">
-        <v>9387600</v>
+        <v>8723000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45968</v>
+        <v>45980</v>
       </c>
       <c r="B99" t="n">
-        <v>154064</v>
+        <v>155381</v>
       </c>
       <c r="C99" t="n">
-        <v>154066</v>
+        <v>156522</v>
       </c>
       <c r="D99" t="n">
-        <v>152368</v>
+        <v>155212</v>
       </c>
       <c r="E99" t="n">
-        <v>153339</v>
+        <v>156522</v>
       </c>
       <c r="F99" t="n">
-        <v>9474100</v>
+        <v>8815200</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45971</v>
+        <v>45982</v>
       </c>
       <c r="B100" t="n">
-        <v>155257</v>
+        <v>154770</v>
       </c>
       <c r="C100" t="n">
-        <v>155601</v>
+        <v>155387</v>
       </c>
       <c r="D100" t="n">
-        <v>154058</v>
+        <v>153571</v>
       </c>
       <c r="E100" t="n">
-        <v>154061</v>
+        <v>155381</v>
       </c>
       <c r="F100" t="n">
-        <v>7751600</v>
+        <v>7848000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45972</v>
+        <v>45985</v>
       </c>
       <c r="B101" t="n">
-        <v>157749</v>
+        <v>155278</v>
       </c>
       <c r="C101" t="n">
-        <v>158467</v>
+        <v>155832</v>
       </c>
       <c r="D101" t="n">
-        <v>155252</v>
+        <v>154529</v>
       </c>
       <c r="E101" t="n">
-        <v>155257</v>
+        <v>154769</v>
       </c>
       <c r="F101" t="n">
-        <v>12876000</v>
+        <v>9277600</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45973</v>
+        <v>45986</v>
       </c>
       <c r="B102" t="n">
-        <v>157633</v>
+        <v>155910</v>
       </c>
       <c r="C102" t="n">
-        <v>158134</v>
+        <v>156373</v>
       </c>
       <c r="D102" t="n">
-        <v>156560</v>
+        <v>154821</v>
       </c>
       <c r="E102" t="n">
-        <v>157749</v>
+        <v>155278</v>
       </c>
       <c r="F102" t="n">
-        <v>11226600</v>
+        <v>6929400</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45974</v>
+        <v>45987</v>
       </c>
       <c r="B103" t="n">
-        <v>157162</v>
+        <v>158555</v>
       </c>
       <c r="C103" t="n">
-        <v>158319</v>
+        <v>158714</v>
       </c>
       <c r="D103" t="n">
-        <v>156509</v>
+        <v>155914</v>
       </c>
       <c r="E103" t="n">
-        <v>157633</v>
+        <v>155915</v>
       </c>
       <c r="F103" t="n">
-        <v>10560800</v>
+        <v>8596500</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45975</v>
+        <v>45988</v>
       </c>
       <c r="B104" t="n">
-        <v>157739</v>
+        <v>158292</v>
       </c>
       <c r="C104" t="n">
-        <v>158366</v>
+        <v>158864</v>
       </c>
       <c r="D104" t="n">
-        <v>156656</v>
+        <v>158167</v>
       </c>
       <c r="E104" t="n">
-        <v>157162</v>
+        <v>158554</v>
       </c>
       <c r="F104" t="n">
-        <v>7977300</v>
+        <v>3121400</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45978</v>
+        <v>45989</v>
       </c>
       <c r="B105" t="n">
-        <v>156993</v>
+        <v>159072</v>
       </c>
       <c r="C105" t="n">
-        <v>157901</v>
+        <v>159689</v>
       </c>
       <c r="D105" t="n">
-        <v>156568</v>
+        <v>158078</v>
       </c>
       <c r="E105" t="n">
-        <v>157742</v>
+        <v>158358</v>
       </c>
       <c r="F105" t="n">
-        <v>8419200</v>
+        <v>8017000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45979</v>
+        <v>45992</v>
       </c>
       <c r="B106" t="n">
-        <v>156522</v>
+        <v>158611</v>
       </c>
       <c r="C106" t="n">
-        <v>157040</v>
+        <v>159224</v>
       </c>
       <c r="D106" t="n">
-        <v>155834</v>
+        <v>158030</v>
       </c>
       <c r="E106" t="n">
-        <v>156990</v>
+        <v>159074</v>
       </c>
       <c r="F106" t="n">
-        <v>8723000</v>
+        <v>7504300</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45980</v>
+        <v>45993</v>
       </c>
       <c r="B107" t="n">
-        <v>155381</v>
+        <v>161092</v>
       </c>
       <c r="C107" t="n">
-        <v>156522</v>
+        <v>161092</v>
       </c>
       <c r="D107" t="n">
-        <v>155212</v>
+        <v>158612</v>
       </c>
       <c r="E107" t="n">
-        <v>156522</v>
+        <v>158612</v>
       </c>
       <c r="F107" t="n">
-        <v>8815200</v>
+        <v>8430000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45982</v>
+        <v>45994</v>
       </c>
       <c r="B108" t="n">
-        <v>154770</v>
+        <v>161755</v>
       </c>
       <c r="C108" t="n">
-        <v>155387</v>
+        <v>161964</v>
       </c>
       <c r="D108" t="n">
-        <v>153571</v>
+        <v>161093</v>
       </c>
       <c r="E108" t="n">
-        <v>155381</v>
+        <v>161094</v>
       </c>
       <c r="F108" t="n">
-        <v>7848000</v>
+        <v>8292000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45985</v>
+        <v>45995</v>
       </c>
       <c r="B109" t="n">
-        <v>155278</v>
+        <v>164456</v>
       </c>
       <c r="C109" t="n">
-        <v>155832</v>
+        <v>164551</v>
       </c>
       <c r="D109" t="n">
-        <v>154529</v>
+        <v>161759</v>
       </c>
       <c r="E109" t="n">
-        <v>154769</v>
+        <v>161760</v>
       </c>
       <c r="F109" t="n">
-        <v>9277600</v>
+        <v>10592300</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45986</v>
+        <v>45996</v>
       </c>
       <c r="B110" t="n">
-        <v>155910</v>
+        <v>157369</v>
       </c>
       <c r="C110" t="n">
-        <v>156373</v>
+        <v>165036</v>
       </c>
       <c r="D110" t="n">
-        <v>154821</v>
+        <v>157007</v>
       </c>
       <c r="E110" t="n">
-        <v>155278</v>
+        <v>164461</v>
       </c>
       <c r="F110" t="n">
-        <v>6929400</v>
+        <v>14529000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45987</v>
+        <v>45999</v>
       </c>
       <c r="B111" t="n">
-        <v>158555</v>
+        <v>158187</v>
       </c>
       <c r="C111" t="n">
-        <v>158714</v>
+        <v>159235</v>
       </c>
       <c r="D111" t="n">
-        <v>155914</v>
+        <v>157369</v>
       </c>
       <c r="E111" t="n">
-        <v>155915</v>
+        <v>157369</v>
       </c>
       <c r="F111" t="n">
-        <v>8596500</v>
+        <v>9024100</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45988</v>
+        <v>46000</v>
       </c>
       <c r="B112" t="n">
-        <v>158292</v>
+        <v>157981</v>
       </c>
       <c r="C112" t="n">
-        <v>158864</v>
+        <v>158851</v>
       </c>
       <c r="D112" t="n">
-        <v>158167</v>
+        <v>155188</v>
       </c>
       <c r="E112" t="n">
-        <v>158554</v>
+        <v>158187</v>
       </c>
       <c r="F112" t="n">
-        <v>3121400</v>
+        <v>8703800</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45989</v>
+        <v>46001</v>
       </c>
       <c r="B113" t="n">
-        <v>159072</v>
+        <v>159075</v>
       </c>
       <c r="C113" t="n">
-        <v>159689</v>
+        <v>159691</v>
       </c>
       <c r="D113" t="n">
-        <v>158078</v>
+        <v>157628</v>
       </c>
       <c r="E113" t="n">
-        <v>158358</v>
+        <v>157984</v>
       </c>
       <c r="F113" t="n">
-        <v>8017000</v>
+        <v>8239900</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45992</v>
+        <v>46002</v>
       </c>
       <c r="B114" t="n">
-        <v>158611</v>
+        <v>159189</v>
       </c>
       <c r="C114" t="n">
-        <v>159224</v>
+        <v>159850</v>
       </c>
       <c r="D114" t="n">
-        <v>158030</v>
+        <v>158098</v>
       </c>
       <c r="E114" t="n">
-        <v>159074</v>
+        <v>159072</v>
       </c>
       <c r="F114" t="n">
-        <v>7504300</v>
+        <v>7018000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="B115" t="n">
-        <v>161092</v>
+        <v>160766</v>
       </c>
       <c r="C115" t="n">
-        <v>161092</v>
+        <v>161263</v>
       </c>
       <c r="D115" t="n">
-        <v>158612</v>
+        <v>159189</v>
       </c>
       <c r="E115" t="n">
-        <v>158612</v>
+        <v>159189</v>
       </c>
       <c r="F115" t="n">
-        <v>8430000</v>
+        <v>7671200</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45994</v>
+        <v>46006</v>
       </c>
       <c r="B116" t="n">
-        <v>161755</v>
+        <v>162482</v>
       </c>
       <c r="C116" t="n">
-        <v>161964</v>
+        <v>163073</v>
       </c>
       <c r="D116" t="n">
-        <v>161093</v>
+        <v>160766</v>
       </c>
       <c r="E116" t="n">
-        <v>161094</v>
+        <v>160766</v>
       </c>
       <c r="F116" t="n">
-        <v>8292000</v>
+        <v>8229000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="B117" t="n">
-        <v>164456</v>
+        <v>158578</v>
       </c>
       <c r="C117" t="n">
-        <v>164551</v>
+        <v>162482</v>
       </c>
       <c r="D117" t="n">
-        <v>161759</v>
+        <v>158558</v>
       </c>
       <c r="E117" t="n">
-        <v>161760</v>
+        <v>162482</v>
       </c>
       <c r="F117" t="n">
-        <v>10592300</v>
+        <v>9920300</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>45996</v>
+        <v>46008</v>
       </c>
       <c r="B118" t="n">
-        <v>157369</v>
+        <v>157327</v>
       </c>
       <c r="C118" t="n">
-        <v>165036</v>
+        <v>158611</v>
       </c>
       <c r="D118" t="n">
-        <v>157007</v>
+        <v>156351</v>
       </c>
       <c r="E118" t="n">
-        <v>164461</v>
+        <v>158578</v>
       </c>
       <c r="F118" t="n">
-        <v>14529000</v>
+        <v>11344300</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>45999</v>
+        <v>46009</v>
       </c>
       <c r="B119" t="n">
-        <v>158187</v>
+        <v>157923</v>
       </c>
       <c r="C119" t="n">
-        <v>159235</v>
+        <v>158496</v>
       </c>
       <c r="D119" t="n">
-        <v>157369</v>
+        <v>157124</v>
       </c>
       <c r="E119" t="n">
-        <v>157369</v>
+        <v>157327</v>
       </c>
       <c r="F119" t="n">
-        <v>9024100</v>
+        <v>7800100</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46000</v>
+        <v>46010</v>
       </c>
       <c r="B120" t="n">
-        <v>157981</v>
+        <v>158473</v>
       </c>
       <c r="C120" t="n">
-        <v>158851</v>
+        <v>159552</v>
       </c>
       <c r="D120" t="n">
-        <v>155188</v>
+        <v>157906</v>
       </c>
       <c r="E120" t="n">
-        <v>158187</v>
+        <v>157928</v>
       </c>
       <c r="F120" t="n">
-        <v>8703800</v>
+        <v>9946500</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46001</v>
+        <v>46013</v>
       </c>
       <c r="B121" t="n">
-        <v>159075</v>
+        <v>158142</v>
       </c>
       <c r="C121" t="n">
-        <v>159691</v>
+        <v>158634</v>
       </c>
       <c r="D121" t="n">
-        <v>157628</v>
+        <v>157306</v>
       </c>
       <c r="E121" t="n">
-        <v>157984</v>
+        <v>158480</v>
       </c>
       <c r="F121" t="n">
-        <v>8239900</v>
+        <v>8424000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="B122" t="n">
-        <v>159189</v>
+        <v>160456</v>
       </c>
       <c r="C122" t="n">
-        <v>159850</v>
+        <v>160456</v>
       </c>
       <c r="D122" t="n">
-        <v>158098</v>
+        <v>158144</v>
       </c>
       <c r="E122" t="n">
-        <v>159072</v>
+        <v>158144</v>
       </c>
       <c r="F122" t="n">
-        <v>7018000</v>
+        <v>6569800</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46003</v>
+        <v>46017</v>
       </c>
       <c r="B123" t="n">
-        <v>160766</v>
+        <v>160897</v>
       </c>
       <c r="C123" t="n">
-        <v>161263</v>
+        <v>160913</v>
       </c>
       <c r="D123" t="n">
-        <v>159189</v>
+        <v>159359</v>
       </c>
       <c r="E123" t="n">
-        <v>159189</v>
+        <v>160456</v>
       </c>
       <c r="F123" t="n">
-        <v>7671200</v>
+        <v>4790000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46006</v>
+        <v>46020</v>
       </c>
       <c r="B124" t="n">
-        <v>162482</v>
+        <v>160490</v>
       </c>
       <c r="C124" t="n">
-        <v>163073</v>
+        <v>161133</v>
       </c>
       <c r="D124" t="n">
-        <v>160766</v>
+        <v>159702</v>
       </c>
       <c r="E124" t="n">
-        <v>160766</v>
+        <v>160897</v>
       </c>
       <c r="F124" t="n">
-        <v>8229000</v>
+        <v>5605600</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="B125" t="n">
-        <v>158578</v>
+        <v>161125</v>
       </c>
       <c r="C125" t="n">
-        <v>162482</v>
+        <v>162075</v>
       </c>
       <c r="D125" t="n">
-        <v>158558</v>
+        <v>160491</v>
       </c>
       <c r="E125" t="n">
-        <v>162482</v>
+        <v>160491</v>
       </c>
       <c r="F125" t="n">
-        <v>9920300</v>
+        <v>5870100</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46008</v>
+        <v>46024</v>
       </c>
       <c r="B126" t="n">
-        <v>157327</v>
+        <v>160539</v>
       </c>
       <c r="C126" t="n">
-        <v>158611</v>
+        <v>161957</v>
       </c>
       <c r="D126" t="n">
-        <v>156351</v>
+        <v>160059</v>
       </c>
       <c r="E126" t="n">
-        <v>158578</v>
+        <v>161124</v>
       </c>
       <c r="F126" t="n">
-        <v>11344300</v>
+        <v>7459400</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46009</v>
+        <v>46027</v>
       </c>
       <c r="B127" t="n">
-        <v>157923</v>
+        <v>161870</v>
       </c>
       <c r="C127" t="n">
-        <v>158496</v>
+        <v>162166</v>
       </c>
       <c r="D127" t="n">
-        <v>157124</v>
+        <v>160215</v>
       </c>
       <c r="E127" t="n">
-        <v>157327</v>
+        <v>160542</v>
       </c>
       <c r="F127" t="n">
-        <v>7800100</v>
+        <v>7985200</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46010</v>
+        <v>46028</v>
       </c>
       <c r="B128" t="n">
-        <v>158473</v>
+        <v>163664</v>
       </c>
       <c r="C128" t="n">
-        <v>159552</v>
+        <v>164135</v>
       </c>
       <c r="D128" t="n">
-        <v>157906</v>
+        <v>161870</v>
       </c>
       <c r="E128" t="n">
-        <v>157928</v>
+        <v>161870</v>
       </c>
       <c r="F128" t="n">
-        <v>9946500</v>
+        <v>8412600</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46013</v>
+        <v>46029</v>
       </c>
       <c r="B129" t="n">
-        <v>158142</v>
+        <v>161975</v>
       </c>
       <c r="C129" t="n">
-        <v>158634</v>
+        <v>163661</v>
       </c>
       <c r="D129" t="n">
-        <v>157306</v>
+        <v>161746</v>
       </c>
       <c r="E129" t="n">
-        <v>158480</v>
+        <v>163661</v>
       </c>
       <c r="F129" t="n">
-        <v>8424000</v>
+        <v>8846600</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46014</v>
+        <v>46030</v>
       </c>
       <c r="B130" t="n">
-        <v>160456</v>
+        <v>162937</v>
       </c>
       <c r="C130" t="n">
-        <v>160456</v>
+        <v>162937</v>
       </c>
       <c r="D130" t="n">
-        <v>158144</v>
+        <v>161748</v>
       </c>
       <c r="E130" t="n">
-        <v>158144</v>
+        <v>161975</v>
       </c>
       <c r="F130" t="n">
-        <v>6569800</v>
+        <v>8607700</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46017</v>
+        <v>46031</v>
       </c>
       <c r="B131" t="n">
-        <v>160897</v>
+        <v>163370</v>
       </c>
       <c r="C131" t="n">
-        <v>160913</v>
+        <v>164263</v>
       </c>
       <c r="D131" t="n">
-        <v>159359</v>
+        <v>162638</v>
       </c>
       <c r="E131" t="n">
-        <v>160456</v>
+        <v>162938</v>
       </c>
       <c r="F131" t="n">
-        <v>4790000</v>
+        <v>8301300</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46020</v>
+        <v>46034</v>
       </c>
       <c r="B132" t="n">
-        <v>160490</v>
+        <v>163150</v>
       </c>
       <c r="C132" t="n">
-        <v>161133</v>
+        <v>163493</v>
       </c>
       <c r="D132" t="n">
-        <v>159702</v>
+        <v>162277</v>
       </c>
       <c r="E132" t="n">
-        <v>160897</v>
+        <v>163370</v>
       </c>
       <c r="F132" t="n">
-        <v>5605600</v>
+        <v>6896600</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46021</v>
+        <v>46035</v>
       </c>
       <c r="B133" t="n">
-        <v>161125</v>
+        <v>161973</v>
       </c>
       <c r="C133" t="n">
-        <v>162075</v>
+        <v>163146</v>
       </c>
       <c r="D133" t="n">
-        <v>160491</v>
+        <v>161765</v>
       </c>
       <c r="E133" t="n">
-        <v>160491</v>
+        <v>163146</v>
       </c>
       <c r="F133" t="n">
-        <v>5870100</v>
+        <v>9668600</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46024</v>
+        <v>46036</v>
       </c>
       <c r="B134" t="n">
-        <v>160539</v>
+        <v>165146</v>
       </c>
       <c r="C134" t="n">
-        <v>161957</v>
+        <v>165147</v>
       </c>
       <c r="D134" t="n">
-        <v>160059</v>
+        <v>161974</v>
       </c>
       <c r="E134" t="n">
-        <v>161124</v>
+        <v>161974</v>
       </c>
       <c r="F134" t="n">
-        <v>7459400</v>
+        <v>9928900</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="B135" t="n">
-        <v>161870</v>
+        <v>165568</v>
       </c>
       <c r="C135" t="n">
-        <v>162166</v>
+        <v>166070</v>
       </c>
       <c r="D135" t="n">
-        <v>160215</v>
+        <v>164833</v>
       </c>
       <c r="E135" t="n">
-        <v>160542</v>
+        <v>165180</v>
       </c>
       <c r="F135" t="n">
-        <v>7985200</v>
+        <v>9406500</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46028</v>
+        <v>46038</v>
       </c>
       <c r="B136" t="n">
-        <v>163664</v>
+        <v>164800</v>
       </c>
       <c r="C136" t="n">
-        <v>164135</v>
+        <v>165872</v>
       </c>
       <c r="D136" t="n">
-        <v>161870</v>
+        <v>164100</v>
       </c>
       <c r="E136" t="n">
-        <v>161870</v>
+        <v>165557</v>
       </c>
       <c r="F136" t="n">
-        <v>8412600</v>
+        <v>11489200</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="B137" t="n">
-        <v>161975</v>
+        <v>164849</v>
       </c>
       <c r="C137" t="n">
-        <v>163661</v>
+        <v>165155</v>
       </c>
       <c r="D137" t="n">
-        <v>161746</v>
+        <v>164265</v>
       </c>
       <c r="E137" t="n">
-        <v>163661</v>
+        <v>164800</v>
       </c>
       <c r="F137" t="n">
-        <v>8846600</v>
+        <v>4804300</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46030</v>
+        <v>46042</v>
       </c>
       <c r="B138" t="n">
-        <v>162937</v>
+        <v>166277</v>
       </c>
       <c r="C138" t="n">
-        <v>162937</v>
+        <v>166468</v>
       </c>
       <c r="D138" t="n">
-        <v>161748</v>
+        <v>163575</v>
       </c>
       <c r="E138" t="n">
-        <v>161975</v>
+        <v>164846</v>
       </c>
       <c r="F138" t="n">
-        <v>8607700</v>
+        <v>8369200</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="B139" t="n">
-        <v>163370</v>
+        <v>171817</v>
       </c>
       <c r="C139" t="n">
-        <v>164263</v>
+        <v>171969</v>
       </c>
       <c r="D139" t="n">
-        <v>162638</v>
+        <v>166278</v>
       </c>
       <c r="E139" t="n">
-        <v>162938</v>
+        <v>166278</v>
       </c>
       <c r="F139" t="n">
-        <v>8301300</v>
+        <v>14067700</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46034</v>
+        <v>46044</v>
       </c>
       <c r="B140" t="n">
-        <v>163150</v>
+        <v>175589</v>
       </c>
       <c r="C140" t="n">
-        <v>163493</v>
+        <v>177742</v>
       </c>
       <c r="D140" t="n">
-        <v>162277</v>
+        <v>171817</v>
       </c>
       <c r="E140" t="n">
-        <v>163370</v>
+        <v>171817</v>
       </c>
       <c r="F140" t="n">
-        <v>6896600</v>
+        <v>14023500</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46035</v>
+        <v>46045</v>
       </c>
       <c r="B141" t="n">
-        <v>161973</v>
+        <v>178859</v>
       </c>
       <c r="C141" t="n">
-        <v>163146</v>
+        <v>180532</v>
       </c>
       <c r="D141" t="n">
-        <v>161765</v>
+        <v>175590</v>
       </c>
       <c r="E141" t="n">
-        <v>163146</v>
+        <v>175590</v>
       </c>
       <c r="F141" t="n">
-        <v>9668600</v>
+        <v>11778000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46036</v>
+        <v>46048</v>
       </c>
       <c r="B142" t="n">
-        <v>165146</v>
+        <v>178721</v>
       </c>
       <c r="C142" t="n">
-        <v>165147</v>
+        <v>179543</v>
       </c>
       <c r="D142" t="n">
-        <v>161974</v>
+        <v>177694</v>
       </c>
       <c r="E142" t="n">
-        <v>161974</v>
+        <v>178859</v>
       </c>
       <c r="F142" t="n">
-        <v>9928900</v>
+        <v>9569200</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46037</v>
+        <v>46049</v>
       </c>
       <c r="B143" t="n">
-        <v>165568</v>
+        <v>181919</v>
       </c>
       <c r="C143" t="n">
-        <v>166070</v>
+        <v>183360</v>
       </c>
       <c r="D143" t="n">
-        <v>164833</v>
+        <v>178853</v>
       </c>
       <c r="E143" t="n">
-        <v>165180</v>
+        <v>178853</v>
       </c>
       <c r="F143" t="n">
-        <v>9406500</v>
+        <v>11340800</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46038</v>
+        <v>46050</v>
       </c>
       <c r="B144" t="n">
-        <v>164800</v>
+        <v>184691</v>
       </c>
       <c r="C144" t="n">
-        <v>165872</v>
+        <v>185065</v>
       </c>
       <c r="D144" t="n">
-        <v>164100</v>
+        <v>181921</v>
       </c>
       <c r="E144" t="n">
-        <v>165557</v>
+        <v>181921</v>
       </c>
       <c r="F144" t="n">
-        <v>11489200</v>
+        <v>11856200</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46041</v>
+        <v>46051</v>
       </c>
       <c r="B145" t="n">
-        <v>164849</v>
+        <v>183134</v>
       </c>
       <c r="C145" t="n">
-        <v>165155</v>
+        <v>186450</v>
       </c>
       <c r="D145" t="n">
-        <v>164265</v>
+        <v>181567</v>
       </c>
       <c r="E145" t="n">
-        <v>164800</v>
+        <v>184692</v>
       </c>
       <c r="F145" t="n">
-        <v>4804300</v>
+        <v>12945700</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46042</v>
+        <v>46052</v>
       </c>
       <c r="B146" t="n">
-        <v>166277</v>
+        <v>181364</v>
       </c>
       <c r="C146" t="n">
-        <v>166468</v>
+        <v>183620</v>
       </c>
       <c r="D146" t="n">
-        <v>163575</v>
+        <v>180089</v>
       </c>
       <c r="E146" t="n">
-        <v>164846</v>
+        <v>183133</v>
       </c>
       <c r="F146" t="n">
-        <v>8369200</v>
+        <v>11105300</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46043</v>
+        <v>46055</v>
       </c>
       <c r="B147" t="n">
-        <v>171817</v>
+        <v>182793</v>
       </c>
       <c r="C147" t="n">
-        <v>171969</v>
+        <v>182890</v>
       </c>
       <c r="D147" t="n">
-        <v>166278</v>
+        <v>181348</v>
       </c>
       <c r="E147" t="n">
-        <v>166278</v>
+        <v>181369</v>
       </c>
       <c r="F147" t="n">
-        <v>14067700</v>
+        <v>8740500</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46044</v>
+        <v>46056</v>
       </c>
       <c r="B148" t="n">
-        <v>175589</v>
+        <v>185674</v>
       </c>
       <c r="C148" t="n">
-        <v>177742</v>
+        <v>187334</v>
       </c>
       <c r="D148" t="n">
-        <v>171817</v>
+        <v>182816</v>
       </c>
       <c r="E148" t="n">
-        <v>171817</v>
+        <v>182816</v>
       </c>
       <c r="F148" t="n">
-        <v>14023500</v>
+        <v>10758800</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46045</v>
+        <v>46057</v>
       </c>
       <c r="B149" t="n">
-        <v>178859</v>
+        <v>181708</v>
       </c>
       <c r="C149" t="n">
-        <v>180532</v>
+        <v>185671</v>
       </c>
       <c r="D149" t="n">
-        <v>175590</v>
+        <v>180269</v>
       </c>
       <c r="E149" t="n">
-        <v>175590</v>
+        <v>185671</v>
       </c>
       <c r="F149" t="n">
-        <v>11778000</v>
+        <v>10728100</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46048</v>
+        <v>46058</v>
       </c>
       <c r="B150" t="n">
-        <v>178721</v>
+        <v>182127</v>
       </c>
       <c r="C150" t="n">
-        <v>179543</v>
+        <v>184017</v>
       </c>
       <c r="D150" t="n">
-        <v>177694</v>
+        <v>181569</v>
       </c>
       <c r="E150" t="n">
-        <v>178859</v>
+        <v>181709</v>
       </c>
       <c r="F150" t="n">
-        <v>9569200</v>
+        <v>9832100</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B151" t="n">
-        <v>181919</v>
+        <v>182950</v>
       </c>
       <c r="C151" t="n">
-        <v>183360</v>
+        <v>183262</v>
       </c>
       <c r="D151" t="n">
-        <v>178853</v>
+        <v>181391</v>
       </c>
       <c r="E151" t="n">
-        <v>178853</v>
+        <v>182128</v>
       </c>
       <c r="F151" t="n">
-        <v>11340800</v>
+        <v>9896700</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46050</v>
+        <v>46062</v>
       </c>
       <c r="B152" t="n">
-        <v>184691</v>
+        <v>186241</v>
       </c>
       <c r="C152" t="n">
-        <v>185065</v>
+        <v>186460</v>
       </c>
       <c r="D152" t="n">
-        <v>181921</v>
+        <v>182950</v>
       </c>
       <c r="E152" t="n">
-        <v>181921</v>
+        <v>182950</v>
       </c>
       <c r="F152" t="n">
-        <v>11856200</v>
+        <v>8921800</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46051</v>
+        <v>46063</v>
       </c>
       <c r="B153" t="n">
-        <v>183134</v>
+        <v>185929</v>
       </c>
       <c r="C153" t="n">
-        <v>186450</v>
+        <v>186959</v>
       </c>
       <c r="D153" t="n">
-        <v>181567</v>
+        <v>185083</v>
       </c>
       <c r="E153" t="n">
-        <v>184692</v>
+        <v>186241</v>
       </c>
       <c r="F153" t="n">
-        <v>12945700</v>
+        <v>10298000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="B154" t="n">
-        <v>181364</v>
+        <v>189699</v>
       </c>
       <c r="C154" t="n">
-        <v>183620</v>
+        <v>190561</v>
       </c>
       <c r="D154" t="n">
-        <v>180089</v>
+        <v>185936</v>
       </c>
       <c r="E154" t="n">
-        <v>183133</v>
+        <v>185936</v>
       </c>
       <c r="F154" t="n">
-        <v>11105300</v>
+        <v>11642200</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46055</v>
+        <v>46065</v>
       </c>
       <c r="B155" t="n">
-        <v>182793</v>
+        <v>187766</v>
       </c>
       <c r="C155" t="n">
-        <v>182890</v>
+        <v>189990</v>
       </c>
       <c r="D155" t="n">
-        <v>181348</v>
+        <v>186959</v>
       </c>
       <c r="E155" t="n">
-        <v>181369</v>
+        <v>189694</v>
       </c>
       <c r="F155" t="n">
-        <v>8740500</v>
+        <v>12361300</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46056</v>
+        <v>46066</v>
       </c>
       <c r="B156" t="n">
-        <v>185674</v>
+        <v>186464</v>
       </c>
       <c r="C156" t="n">
-        <v>187334</v>
+        <v>187766</v>
       </c>
       <c r="D156" t="n">
-        <v>182816</v>
+        <v>183662</v>
       </c>
       <c r="E156" t="n">
-        <v>182816</v>
+        <v>187766</v>
       </c>
       <c r="F156" t="n">
-        <v>10758800</v>
+        <v>11594000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46057</v>
+        <v>46071</v>
       </c>
       <c r="B157" t="n">
-        <v>181708</v>
+        <v>186016</v>
       </c>
       <c r="C157" t="n">
-        <v>185671</v>
+        <v>187657</v>
       </c>
       <c r="D157" t="n">
-        <v>180269</v>
+        <v>185001</v>
       </c>
       <c r="E157" t="n">
-        <v>185671</v>
+        <v>186464</v>
       </c>
       <c r="F157" t="n">
-        <v>10728100</v>
+        <v>7790700</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46058</v>
+        <v>46072</v>
       </c>
       <c r="B158" t="n">
-        <v>182127</v>
+        <v>188534</v>
       </c>
       <c r="C158" t="n">
-        <v>184017</v>
+        <v>188687</v>
       </c>
       <c r="D158" t="n">
-        <v>181569</v>
+        <v>185928</v>
       </c>
       <c r="E158" t="n">
-        <v>181709</v>
+        <v>186020</v>
       </c>
       <c r="F158" t="n">
-        <v>9832100</v>
+        <v>9228700</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="B159" t="n">
-        <v>182950</v>
+        <v>190534</v>
       </c>
       <c r="C159" t="n">
-        <v>183262</v>
+        <v>190727</v>
       </c>
       <c r="D159" t="n">
-        <v>181391</v>
+        <v>186700</v>
       </c>
       <c r="E159" t="n">
-        <v>182128</v>
+        <v>188531</v>
       </c>
       <c r="F159" t="n">
-        <v>9896700</v>
+        <v>9988100</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46062</v>
+        <v>46076</v>
       </c>
       <c r="B160" t="n">
-        <v>186241</v>
+        <v>188854</v>
       </c>
       <c r="C160" t="n">
-        <v>186460</v>
+        <v>191003</v>
       </c>
       <c r="D160" t="n">
-        <v>182950</v>
+        <v>188526</v>
       </c>
       <c r="E160" t="n">
-        <v>182950</v>
+        <v>190532</v>
       </c>
       <c r="F160" t="n">
-        <v>8921800</v>
+        <v>9901300</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46063</v>
+        <v>46077</v>
       </c>
       <c r="B161" t="n">
-        <v>185929</v>
+        <v>191490</v>
       </c>
       <c r="C161" t="n">
-        <v>186959</v>
+        <v>191781</v>
       </c>
       <c r="D161" t="n">
-        <v>185083</v>
+        <v>188855</v>
       </c>
       <c r="E161" t="n">
-        <v>186241</v>
+        <v>188855</v>
       </c>
       <c r="F161" t="n">
-        <v>10298000</v>
+        <v>11037300</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46064</v>
+        <v>46078</v>
       </c>
       <c r="B162" t="n">
-        <v>189699</v>
+        <v>191248</v>
       </c>
       <c r="C162" t="n">
-        <v>190561</v>
+        <v>192624</v>
       </c>
       <c r="D162" t="n">
-        <v>185936</v>
+        <v>190419</v>
       </c>
       <c r="E162" t="n">
-        <v>185936</v>
+        <v>191491</v>
       </c>
       <c r="F162" t="n">
-        <v>11642200</v>
+        <v>9134900</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46065</v>
+        <v>46079</v>
       </c>
       <c r="B163" t="n">
-        <v>187766</v>
+        <v>191005</v>
       </c>
       <c r="C163" t="n">
-        <v>189990</v>
+        <v>191978</v>
       </c>
       <c r="D163" t="n">
-        <v>186959</v>
+        <v>188977</v>
       </c>
       <c r="E163" t="n">
-        <v>189694</v>
+        <v>191248</v>
       </c>
       <c r="F163" t="n">
-        <v>12361300</v>
+        <v>8797400</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="B164" t="n">
-        <v>186464</v>
+        <v>188787</v>
       </c>
       <c r="C164" t="n">
-        <v>187766</v>
+        <v>191005</v>
       </c>
       <c r="D164" t="n">
-        <v>183662</v>
+        <v>188478</v>
       </c>
       <c r="E164" t="n">
-        <v>187766</v>
+        <v>191005</v>
       </c>
       <c r="F164" t="n">
-        <v>11594000</v>
+        <v>11002300</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46071</v>
+        <v>46083</v>
       </c>
       <c r="B165" t="n">
-        <v>186016</v>
+        <v>189307</v>
       </c>
       <c r="C165" t="n">
-        <v>187657</v>
+        <v>190110</v>
       </c>
       <c r="D165" t="n">
-        <v>185001</v>
+        <v>186638</v>
       </c>
       <c r="E165" t="n">
-        <v>186464</v>
+        <v>188786</v>
       </c>
       <c r="F165" t="n">
-        <v>7790700</v>
+        <v>9090200</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46072</v>
+        <v>46084</v>
       </c>
       <c r="B166" t="n">
-        <v>188534</v>
+        <v>183105</v>
       </c>
       <c r="C166" t="n">
-        <v>188687</v>
+        <v>189602</v>
       </c>
       <c r="D166" t="n">
-        <v>185928</v>
+        <v>180518</v>
       </c>
       <c r="E166" t="n">
-        <v>186020</v>
+        <v>189284</v>
       </c>
       <c r="F166" t="n">
-        <v>9228700</v>
+        <v>14367500</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46073</v>
+        <v>46085</v>
       </c>
       <c r="B167" t="n">
-        <v>190534</v>
+        <v>185366</v>
       </c>
       <c r="C167" t="n">
-        <v>190727</v>
+        <v>186306</v>
       </c>
       <c r="D167" t="n">
-        <v>186700</v>
+        <v>183110</v>
       </c>
       <c r="E167" t="n">
-        <v>188531</v>
+        <v>183110</v>
       </c>
       <c r="F167" t="n">
-        <v>9988100</v>
+        <v>9113300</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="B168" t="n">
-        <v>188854</v>
+        <v>180464</v>
       </c>
       <c r="C168" t="n">
-        <v>191003</v>
+        <v>185366</v>
       </c>
       <c r="D168" t="n">
-        <v>188526</v>
+        <v>179895</v>
       </c>
       <c r="E168" t="n">
-        <v>190532</v>
+        <v>185365</v>
       </c>
       <c r="F168" t="n">
-        <v>9901300</v>
+        <v>10596200</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46077</v>
+        <v>46087</v>
       </c>
       <c r="B169" t="n">
-        <v>191490</v>
+        <v>179365</v>
       </c>
       <c r="C169" t="n">
-        <v>191781</v>
+        <v>181091</v>
       </c>
       <c r="D169" t="n">
-        <v>188855</v>
+        <v>178557</v>
       </c>
       <c r="E169" t="n">
-        <v>188855</v>
+        <v>180463</v>
       </c>
       <c r="F169" t="n">
-        <v>11037300</v>
+        <v>9918300</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="B170" t="n">
-        <v>191248</v>
+        <v>180915</v>
       </c>
       <c r="C170" t="n">
-        <v>192624</v>
+        <v>181952</v>
       </c>
       <c r="D170" t="n">
-        <v>190419</v>
+        <v>177637</v>
       </c>
       <c r="E170" t="n">
-        <v>191491</v>
+        <v>179367</v>
       </c>
       <c r="F170" t="n">
-        <v>9134900</v>
+        <v>11419300</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46079</v>
+        <v>46091</v>
       </c>
       <c r="B171" t="n">
-        <v>191005</v>
+        <v>183447</v>
       </c>
       <c r="C171" t="n">
-        <v>191978</v>
+        <v>185324</v>
       </c>
       <c r="D171" t="n">
-        <v>188977</v>
+        <v>180693</v>
       </c>
       <c r="E171" t="n">
-        <v>191248</v>
+        <v>180921</v>
       </c>
       <c r="F171" t="n">
-        <v>8797400</v>
+        <v>10083000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46080</v>
+        <v>46092</v>
       </c>
       <c r="B172" t="n">
-        <v>188787</v>
+        <v>183969</v>
       </c>
       <c r="C172" t="n">
-        <v>191005</v>
+        <v>185714</v>
       </c>
       <c r="D172" t="n">
-        <v>188478</v>
+        <v>182021</v>
       </c>
       <c r="E172" t="n">
-        <v>191005</v>
+        <v>183446</v>
       </c>
       <c r="F172" t="n">
-        <v>11002300</v>
+        <v>8956100</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46083</v>
+        <v>46093</v>
       </c>
       <c r="B173" t="n">
-        <v>189307</v>
+        <v>179285</v>
       </c>
       <c r="C173" t="n">
-        <v>190110</v>
+        <v>183992</v>
       </c>
       <c r="D173" t="n">
-        <v>186638</v>
+        <v>178495</v>
       </c>
       <c r="E173" t="n">
-        <v>188786</v>
+        <v>183969</v>
       </c>
       <c r="F173" t="n">
-        <v>9090200</v>
+        <v>12075300</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46084</v>
+        <v>46094</v>
       </c>
       <c r="B174" t="n">
-        <v>183105</v>
+        <v>177653</v>
       </c>
       <c r="C174" t="n">
-        <v>189602</v>
+        <v>180996</v>
       </c>
       <c r="D174" t="n">
-        <v>180518</v>
+        <v>177322</v>
       </c>
       <c r="E174" t="n">
-        <v>189284</v>
+        <v>179285</v>
       </c>
       <c r="F174" t="n">
-        <v>14367500</v>
+        <v>9525600</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46085</v>
+        <v>46097</v>
       </c>
       <c r="B175" t="n">
-        <v>185366</v>
+        <v>179875</v>
       </c>
       <c r="C175" t="n">
-        <v>186306</v>
+        <v>181255</v>
       </c>
       <c r="D175" t="n">
-        <v>183110</v>
+        <v>177656</v>
       </c>
       <c r="E175" t="n">
-        <v>183110</v>
+        <v>177656</v>
       </c>
       <c r="F175" t="n">
-        <v>9113300</v>
+        <v>7370100</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46086</v>
+        <v>46098</v>
       </c>
       <c r="B176" t="n">
-        <v>180464</v>
+        <v>180410</v>
       </c>
       <c r="C176" t="n">
-        <v>185366</v>
+        <v>182800</v>
       </c>
       <c r="D176" t="n">
-        <v>179895</v>
+        <v>179850</v>
       </c>
       <c r="E176" t="n">
-        <v>185365</v>
+        <v>179882</v>
       </c>
       <c r="F176" t="n">
-        <v>10596200</v>
+        <v>9332600</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46087</v>
+        <v>46099</v>
       </c>
       <c r="B177" t="n">
-        <v>179365</v>
+        <v>179640</v>
       </c>
       <c r="C177" t="n">
-        <v>181091</v>
+        <v>181551</v>
       </c>
       <c r="D177" t="n">
-        <v>178557</v>
+        <v>179576</v>
       </c>
       <c r="E177" t="n">
-        <v>180463</v>
+        <v>180409</v>
       </c>
       <c r="F177" t="n">
-        <v>9918300</v>
+        <v>9750200</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="B178" t="n">
-        <v>180915</v>
+        <v>180271</v>
       </c>
       <c r="C178" t="n">
-        <v>181952</v>
+        <v>181251</v>
       </c>
       <c r="D178" t="n">
-        <v>177637</v>
+        <v>176296</v>
       </c>
       <c r="E178" t="n">
-        <v>179367</v>
+        <v>179624</v>
       </c>
       <c r="F178" t="n">
-        <v>11419300</v>
+        <v>12560400</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="B179" t="n">
-        <v>183447</v>
+        <v>176219</v>
       </c>
       <c r="C179" t="n">
-        <v>185324</v>
+        <v>180305</v>
       </c>
       <c r="D179" t="n">
-        <v>180693</v>
+        <v>175039</v>
       </c>
       <c r="E179" t="n">
-        <v>180921</v>
+        <v>180262</v>
       </c>
       <c r="F179" t="n">
-        <v>10083000</v>
+        <v>15348900</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46092</v>
+        <v>46104</v>
       </c>
       <c r="B180" t="n">
-        <v>183969</v>
+        <v>181932</v>
       </c>
       <c r="C180" t="n">
-        <v>185714</v>
+        <v>182973</v>
       </c>
       <c r="D180" t="n">
-        <v>182021</v>
+        <v>176221</v>
       </c>
       <c r="E180" t="n">
-        <v>183446</v>
+        <v>176221</v>
       </c>
       <c r="F180" t="n">
-        <v>8956100</v>
+        <v>9874700</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="B181" t="n">
-        <v>179285</v>
+        <v>182509</v>
       </c>
       <c r="C181" t="n">
-        <v>183992</v>
+        <v>182649</v>
       </c>
       <c r="D181" t="n">
-        <v>178495</v>
+        <v>179915</v>
       </c>
       <c r="E181" t="n">
-        <v>183969</v>
+        <v>181932</v>
       </c>
       <c r="F181" t="n">
-        <v>12075300</v>
+        <v>7563900</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="B182" t="n">
-        <v>177653</v>
+        <v>185424</v>
       </c>
       <c r="C182" t="n">
-        <v>180996</v>
+        <v>186401</v>
       </c>
       <c r="D182" t="n">
-        <v>177322</v>
+        <v>182524</v>
       </c>
       <c r="E182" t="n">
-        <v>179285</v>
+        <v>182529</v>
       </c>
       <c r="F182" t="n">
-        <v>9525600</v>
+        <v>9074000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46097</v>
+        <v>46107</v>
       </c>
       <c r="B183" t="n">
-        <v>179875</v>
+        <v>182733</v>
       </c>
       <c r="C183" t="n">
-        <v>181255</v>
+        <v>185424</v>
       </c>
       <c r="D183" t="n">
-        <v>177656</v>
+        <v>182570</v>
       </c>
       <c r="E183" t="n">
-        <v>177656</v>
+        <v>185424</v>
       </c>
       <c r="F183" t="n">
-        <v>7370100</v>
+        <v>7806700</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="B184" t="n">
-        <v>180410</v>
+        <v>181557</v>
       </c>
       <c r="C184" t="n">
-        <v>182800</v>
+        <v>183351</v>
       </c>
       <c r="D184" t="n">
-        <v>179850</v>
+        <v>180976</v>
       </c>
       <c r="E184" t="n">
-        <v>179882</v>
+        <v>182733</v>
       </c>
       <c r="F184" t="n">
-        <v>9332600</v>
+        <v>8073000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46099</v>
+        <v>46111</v>
       </c>
       <c r="B185" t="n">
-        <v>179640</v>
+        <v>182514</v>
       </c>
       <c r="C185" t="n">
-        <v>181551</v>
+        <v>184414</v>
       </c>
       <c r="D185" t="n">
-        <v>179576</v>
+        <v>181560</v>
       </c>
       <c r="E185" t="n">
-        <v>180409</v>
+        <v>181561</v>
       </c>
       <c r="F185" t="n">
-        <v>9750200</v>
+        <v>7704600</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="B186" t="n">
-        <v>180271</v>
+        <v>187462</v>
       </c>
       <c r="C186" t="n">
-        <v>181251</v>
+        <v>187508</v>
       </c>
       <c r="D186" t="n">
-        <v>176296</v>
+        <v>182515</v>
       </c>
       <c r="E186" t="n">
-        <v>179624</v>
+        <v>182515</v>
       </c>
       <c r="F186" t="n">
-        <v>12560400</v>
+        <v>11389100</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46101</v>
+        <v>46113</v>
       </c>
       <c r="B187" t="n">
-        <v>176219</v>
+        <v>187953</v>
       </c>
       <c r="C187" t="n">
-        <v>180305</v>
+        <v>189131</v>
       </c>
       <c r="D187" t="n">
-        <v>175039</v>
+        <v>187256</v>
       </c>
       <c r="E187" t="n">
-        <v>180262</v>
+        <v>187463</v>
       </c>
       <c r="F187" t="n">
-        <v>15348900</v>
+        <v>10556000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46104</v>
+        <v>46114</v>
       </c>
       <c r="B188" t="n">
-        <v>181932</v>
+        <v>188052</v>
       </c>
       <c r="C188" t="n">
-        <v>182973</v>
+        <v>189251</v>
       </c>
       <c r="D188" t="n">
-        <v>176221</v>
+        <v>185214</v>
       </c>
       <c r="E188" t="n">
-        <v>176221</v>
+        <v>187923</v>
       </c>
       <c r="F188" t="n">
-        <v>9874700</v>
+        <v>7082900</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46105</v>
+        <v>46118</v>
       </c>
       <c r="B189" t="n">
-        <v>182509</v>
+        <v>188162</v>
       </c>
       <c r="C189" t="n">
-        <v>182649</v>
+        <v>189220</v>
       </c>
       <c r="D189" t="n">
-        <v>179915</v>
+        <v>187811</v>
       </c>
       <c r="E189" t="n">
-        <v>181932</v>
+        <v>188054</v>
       </c>
       <c r="F189" t="n">
-        <v>7563900</v>
+        <v>5697600</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="B190" t="n">
-        <v>185424</v>
+        <v>188259</v>
       </c>
       <c r="C190" t="n">
-        <v>186401</v>
+        <v>188259</v>
       </c>
       <c r="D190" t="n">
-        <v>182524</v>
+        <v>185885</v>
       </c>
       <c r="E190" t="n">
-        <v>182529</v>
+        <v>188162</v>
       </c>
       <c r="F190" t="n">
-        <v>9074000</v>
+        <v>8753200</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46107</v>
+        <v>46120</v>
       </c>
       <c r="B191" t="n">
-        <v>182733</v>
+        <v>192201</v>
       </c>
       <c r="C191" t="n">
-        <v>185424</v>
+        <v>193759</v>
       </c>
       <c r="D191" t="n">
-        <v>182570</v>
+        <v>188260</v>
       </c>
       <c r="E191" t="n">
-        <v>185424</v>
+        <v>188261</v>
       </c>
       <c r="F191" t="n">
-        <v>7806700</v>
+        <v>12594000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46108</v>
+        <v>46121</v>
       </c>
       <c r="B192" t="n">
-        <v>181557</v>
+        <v>195129</v>
       </c>
       <c r="C192" t="n">
-        <v>183351</v>
+        <v>195514</v>
       </c>
       <c r="D192" t="n">
-        <v>180976</v>
+        <v>192206</v>
       </c>
       <c r="E192" t="n">
-        <v>182733</v>
+        <v>192206</v>
       </c>
       <c r="F192" t="n">
-        <v>8073000</v>
+        <v>9382900</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46111</v>
+        <v>46122</v>
       </c>
       <c r="B193" t="n">
-        <v>182514</v>
+        <v>197324</v>
       </c>
       <c r="C193" t="n">
-        <v>184414</v>
+        <v>197554</v>
       </c>
       <c r="D193" t="n">
-        <v>181560</v>
+        <v>195129</v>
       </c>
       <c r="E193" t="n">
-        <v>181561</v>
+        <v>195130</v>
       </c>
       <c r="F193" t="n">
-        <v>7704600</v>
+        <v>9661000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46112</v>
+        <v>46125</v>
       </c>
       <c r="B194" t="n">
-        <v>187462</v>
+        <v>198001</v>
       </c>
       <c r="C194" t="n">
-        <v>187508</v>
+        <v>198173</v>
       </c>
       <c r="D194" t="n">
-        <v>182515</v>
+        <v>196223</v>
       </c>
       <c r="E194" t="n">
-        <v>182515</v>
+        <v>197324</v>
       </c>
       <c r="F194" t="n">
-        <v>11389100</v>
+        <v>9947000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="B195" t="n">
-        <v>187953</v>
+        <v>198657</v>
       </c>
       <c r="C195" t="n">
-        <v>189131</v>
+        <v>199355</v>
       </c>
       <c r="D195" t="n">
-        <v>187256</v>
+        <v>198002</v>
       </c>
       <c r="E195" t="n">
-        <v>187463</v>
+        <v>198002</v>
       </c>
       <c r="F195" t="n">
-        <v>10556000</v>
+        <v>9222400</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46114</v>
+        <v>46127</v>
       </c>
       <c r="B196" t="n">
-        <v>188052</v>
+        <v>197738</v>
       </c>
       <c r="C196" t="n">
-        <v>189251</v>
+        <v>199233</v>
       </c>
       <c r="D196" t="n">
-        <v>185214</v>
+        <v>196966</v>
       </c>
       <c r="E196" t="n">
-        <v>187923</v>
+        <v>198657</v>
       </c>
       <c r="F196" t="n">
-        <v>7082900</v>
+        <v>10709900</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46118</v>
+        <v>46128</v>
       </c>
       <c r="B197" t="n">
-        <v>188162</v>
+        <v>196819</v>
       </c>
       <c r="C197" t="n">
-        <v>189220</v>
+        <v>198587</v>
       </c>
       <c r="D197" t="n">
-        <v>187811</v>
+        <v>196354</v>
       </c>
       <c r="E197" t="n">
-        <v>188054</v>
+        <v>197738</v>
       </c>
       <c r="F197" t="n">
-        <v>5697600</v>
+        <v>9286300</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46119</v>
+        <v>46129</v>
       </c>
       <c r="B198" t="n">
-        <v>188259</v>
+        <v>195734</v>
       </c>
       <c r="C198" t="n">
-        <v>188259</v>
+        <v>198666</v>
       </c>
       <c r="D198" t="n">
-        <v>185885</v>
+        <v>195368</v>
       </c>
       <c r="E198" t="n">
-        <v>188162</v>
+        <v>196819</v>
       </c>
       <c r="F198" t="n">
-        <v>8753200</v>
+        <v>12187300</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46120</v>
+        <v>46132</v>
       </c>
       <c r="B199" t="n">
-        <v>192201</v>
+        <v>196132</v>
       </c>
       <c r="C199" t="n">
-        <v>193759</v>
+        <v>196724</v>
       </c>
       <c r="D199" t="n">
-        <v>188260</v>
+        <v>195282</v>
       </c>
       <c r="E199" t="n">
-        <v>188261</v>
+        <v>195734</v>
       </c>
       <c r="F199" t="n">
-        <v>12594000</v>
+        <v>6767400</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46121</v>
+        <v>46134</v>
       </c>
       <c r="B200" t="n">
-        <v>195129</v>
+        <v>192889</v>
       </c>
       <c r="C200" t="n">
-        <v>195514</v>
+        <v>196132</v>
       </c>
       <c r="D200" t="n">
-        <v>192206</v>
+        <v>192687</v>
       </c>
       <c r="E200" t="n">
-        <v>192206</v>
+        <v>196132</v>
       </c>
       <c r="F200" t="n">
-        <v>9382900</v>
+        <v>8398100</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46122</v>
+        <v>46135</v>
       </c>
       <c r="B201" t="n">
-        <v>197324</v>
+        <v>191378</v>
       </c>
       <c r="C201" t="n">
-        <v>197554</v>
+        <v>193347</v>
       </c>
       <c r="D201" t="n">
-        <v>195129</v>
+        <v>190930</v>
       </c>
       <c r="E201" t="n">
-        <v>195130</v>
+        <v>192889</v>
       </c>
       <c r="F201" t="n">
-        <v>9661000</v>
+        <v>7763400</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="B202" t="n">
-        <v>198001</v>
+        <v>190745</v>
       </c>
       <c r="C202" t="n">
-        <v>198173</v>
+        <v>191390</v>
       </c>
       <c r="D202" t="n">
-        <v>196223</v>
+        <v>189963</v>
       </c>
       <c r="E202" t="n">
-        <v>197324</v>
+        <v>191378</v>
       </c>
       <c r="F202" t="n">
-        <v>9947000</v>
+        <v>7223800</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46126</v>
+        <v>46139</v>
       </c>
       <c r="B203" t="n">
-        <v>198657</v>
+        <v>189579</v>
       </c>
       <c r="C203" t="n">
-        <v>199355</v>
+        <v>191340</v>
       </c>
       <c r="D203" t="n">
-        <v>198002</v>
+        <v>189579</v>
       </c>
       <c r="E203" t="n">
-        <v>198002</v>
+        <v>190745</v>
       </c>
       <c r="F203" t="n">
-        <v>9222400</v>
+        <v>6663800</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="B204" t="n">
-        <v>197738</v>
+        <v>188619</v>
       </c>
       <c r="C204" t="n">
-        <v>199233</v>
+        <v>189579</v>
       </c>
       <c r="D204" t="n">
-        <v>196966</v>
+        <v>187237</v>
       </c>
       <c r="E204" t="n">
-        <v>198657</v>
+        <v>189579</v>
       </c>
       <c r="F204" t="n">
-        <v>10709900</v>
+        <v>7511500</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="B205" t="n">
-        <v>196819</v>
+        <v>184750</v>
       </c>
       <c r="C205" t="n">
-        <v>198587</v>
+        <v>188710</v>
       </c>
       <c r="D205" t="n">
-        <v>196354</v>
+        <v>184504</v>
       </c>
       <c r="E205" t="n">
-        <v>197738</v>
+        <v>188619</v>
       </c>
       <c r="F205" t="n">
-        <v>9286300</v>
+        <v>9054900</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="B206" t="n">
-        <v>195734</v>
+        <v>187318</v>
       </c>
       <c r="C206" t="n">
-        <v>198666</v>
+        <v>187921</v>
       </c>
       <c r="D206" t="n">
-        <v>195368</v>
+        <v>184759</v>
       </c>
       <c r="E206" t="n">
-        <v>196819</v>
+        <v>184759</v>
       </c>
       <c r="F206" t="n">
-        <v>12187300</v>
+        <v>8991200</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="B207" t="n">
-        <v>196132</v>
+        <v>185600</v>
       </c>
       <c r="C207" t="n">
-        <v>196724</v>
+        <v>187666</v>
       </c>
       <c r="D207" t="n">
-        <v>195282</v>
+        <v>185538</v>
       </c>
       <c r="E207" t="n">
-        <v>195734</v>
+        <v>187318</v>
       </c>
       <c r="F207" t="n">
-        <v>6767400</v>
+        <v>7544200</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="B208" t="n">
-        <v>192889</v>
+        <v>186754</v>
       </c>
       <c r="C208" t="n">
-        <v>196132</v>
+        <v>187428</v>
       </c>
       <c r="D208" t="n">
-        <v>192687</v>
+        <v>185364</v>
       </c>
       <c r="E208" t="n">
-        <v>196132</v>
+        <v>185597</v>
       </c>
       <c r="F208" t="n">
-        <v>8398100</v>
+        <v>8631700</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46135</v>
+        <v>46148</v>
       </c>
       <c r="B209" t="n">
-        <v>191378</v>
+        <v>187691</v>
       </c>
       <c r="C209" t="n">
-        <v>193347</v>
+        <v>188674</v>
       </c>
       <c r="D209" t="n">
-        <v>190930</v>
+        <v>186762</v>
       </c>
       <c r="E209" t="n">
-        <v>192889</v>
+        <v>186762</v>
       </c>
       <c r="F209" t="n">
-        <v>7763400</v>
+        <v>8844600</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46136</v>
+        <v>46149</v>
       </c>
       <c r="B210" t="n">
-        <v>190745</v>
+        <v>183218</v>
       </c>
       <c r="C210" t="n">
-        <v>191390</v>
+        <v>187779</v>
       </c>
       <c r="D210" t="n">
-        <v>189963</v>
+        <v>182868</v>
       </c>
       <c r="E210" t="n">
-        <v>191378</v>
+        <v>187690</v>
       </c>
       <c r="F210" t="n">
-        <v>7223800</v>
+        <v>9643100</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="B211" t="n">
-        <v>189579</v>
+        <v>184108</v>
       </c>
       <c r="C211" t="n">
-        <v>191340</v>
+        <v>185585</v>
       </c>
       <c r="D211" t="n">
-        <v>189579</v>
+        <v>183217</v>
       </c>
       <c r="E211" t="n">
-        <v>190745</v>
+        <v>183222</v>
       </c>
       <c r="F211" t="n">
-        <v>6663800</v>
+        <v>9214400</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="B212" t="n">
-        <v>188619</v>
+        <v>181909</v>
       </c>
       <c r="C212" t="n">
-        <v>189579</v>
+        <v>184530</v>
       </c>
       <c r="D212" t="n">
-        <v>187237</v>
+        <v>181615</v>
       </c>
       <c r="E212" t="n">
-        <v>189579</v>
+        <v>184103</v>
       </c>
       <c r="F212" t="n">
-        <v>7511500</v>
+        <v>8780300</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46141</v>
+        <v>46154</v>
       </c>
       <c r="B213" t="n">
-        <v>184750</v>
+        <v>180342</v>
       </c>
       <c r="C213" t="n">
-        <v>188710</v>
+        <v>181897</v>
       </c>
       <c r="D213" t="n">
-        <v>184504</v>
+        <v>179939</v>
       </c>
       <c r="E213" t="n">
-        <v>188619</v>
+        <v>181897</v>
       </c>
       <c r="F213" t="n">
-        <v>9054900</v>
+        <v>9056000</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46142</v>
+        <v>46155</v>
       </c>
       <c r="B214" t="n">
-        <v>187318</v>
+        <v>177098</v>
       </c>
       <c r="C214" t="n">
-        <v>187921</v>
+        <v>180513</v>
       </c>
       <c r="D214" t="n">
-        <v>184759</v>
+        <v>176787</v>
       </c>
       <c r="E214" t="n">
-        <v>184759</v>
+        <v>180342</v>
       </c>
       <c r="F214" t="n">
-        <v>8991200</v>
+        <v>12621300</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="B215" t="n">
-        <v>185600</v>
+        <v>178366</v>
       </c>
       <c r="C215" t="n">
-        <v>187666</v>
+        <v>179476</v>
       </c>
       <c r="D215" t="n">
-        <v>185538</v>
+        <v>177104</v>
       </c>
       <c r="E215" t="n">
-        <v>187318</v>
+        <v>177104</v>
       </c>
       <c r="F215" t="n">
-        <v>7544200</v>
+        <v>9295700</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="B216" t="n">
-        <v>186754</v>
+        <v>177284</v>
       </c>
       <c r="C216" t="n">
-        <v>187428</v>
+        <v>178341</v>
       </c>
       <c r="D216" t="n">
-        <v>185364</v>
+        <v>175417</v>
       </c>
       <c r="E216" t="n">
-        <v>185597</v>
+        <v>178341</v>
       </c>
       <c r="F216" t="n">
-        <v>8631700</v>
+        <v>9772200</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="B217" t="n">
-        <v>187691</v>
+        <v>176976</v>
       </c>
       <c r="C217" t="n">
-        <v>188674</v>
+        <v>177330</v>
       </c>
       <c r="D217" t="n">
-        <v>186762</v>
+        <v>175811</v>
       </c>
       <c r="E217" t="n">
-        <v>186762</v>
+        <v>177281</v>
       </c>
       <c r="F217" t="n">
-        <v>8844600</v>
+        <v>7367400</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="B218" t="n">
-        <v>183218</v>
+        <v>174279</v>
       </c>
       <c r="C218" t="n">
-        <v>187779</v>
+        <v>176973</v>
       </c>
       <c r="D218" t="n">
-        <v>182868</v>
+        <v>173544</v>
       </c>
       <c r="E218" t="n">
-        <v>187690</v>
+        <v>176973</v>
       </c>
       <c r="F218" t="n">
-        <v>9643100</v>
+        <v>9086100</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="B219" t="n">
-        <v>184108</v>
+        <v>177356</v>
       </c>
       <c r="C219" t="n">
-        <v>185585</v>
+        <v>178199</v>
       </c>
       <c r="D219" t="n">
-        <v>183217</v>
+        <v>174279</v>
       </c>
       <c r="E219" t="n">
-        <v>183222</v>
+        <v>174279</v>
       </c>
       <c r="F219" t="n">
-        <v>9214400</v>
+        <v>9365700</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B220" t="n">
-        <v>181909</v>
+        <v>177650</v>
       </c>
       <c r="C220" t="n">
-        <v>184530</v>
+        <v>178547</v>
       </c>
       <c r="D220" t="n">
-        <v>181615</v>
+        <v>175805</v>
       </c>
       <c r="E220" t="n">
-        <v>184103</v>
+        <v>177352</v>
       </c>
       <c r="F220" t="n">
-        <v>8780300</v>
+        <v>7354500</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B221" t="n">
-        <v>180342</v>
+        <v>176210</v>
       </c>
       <c r="C221" t="n">
-        <v>181897</v>
+        <v>177649</v>
       </c>
       <c r="D221" t="n">
-        <v>179939</v>
+        <v>174893</v>
       </c>
       <c r="E221" t="n">
-        <v>181897</v>
+        <v>177649</v>
       </c>
       <c r="F221" t="n">
-        <v>9056000</v>
+        <v>6760900</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B222" t="n">
-        <v>177098</v>
+        <v>177359</v>
       </c>
       <c r="C222" t="n">
-        <v>180513</v>
+        <v>177512</v>
       </c>
       <c r="D222" t="n">
-        <v>176787</v>
+        <v>176210</v>
       </c>
       <c r="E222" t="n">
-        <v>180342</v>
+        <v>176210</v>
       </c>
       <c r="F222" t="n">
-        <v>12621300</v>
+        <v>2377600</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="B223" t="n">
-        <v>178366</v>
+        <v>176589</v>
       </c>
       <c r="C223" t="n">
-        <v>179476</v>
+        <v>177816</v>
       </c>
       <c r="D223" t="n">
-        <v>177104</v>
+        <v>175516</v>
       </c>
       <c r="E223" t="n">
-        <v>177104</v>
+        <v>177816</v>
       </c>
       <c r="F223" t="n">
-        <v>9295700</v>
+        <v>7402600</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="B224" t="n">
-        <v>177284</v>
+        <v>175744</v>
       </c>
       <c r="C224" t="n">
-        <v>178341</v>
+        <v>177640</v>
       </c>
       <c r="D224" t="n">
-        <v>175417</v>
+        <v>175555</v>
       </c>
       <c r="E224" t="n">
-        <v>178341</v>
+        <v>176602</v>
       </c>
       <c r="F224" t="n">
-        <v>9772200</v>
+        <v>7310400</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="B225" t="n">
-        <v>176976</v>
+        <v>175063</v>
       </c>
       <c r="C225" t="n">
-        <v>177330</v>
+        <v>176627</v>
       </c>
       <c r="D225" t="n">
-        <v>175811</v>
+        <v>174686</v>
       </c>
       <c r="E225" t="n">
-        <v>177281</v>
+        <v>175744</v>
       </c>
       <c r="F225" t="n">
-        <v>7367400</v>
+        <v>7376200</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="B226" t="n">
-        <v>174279</v>
+        <v>173788</v>
       </c>
       <c r="C226" t="n">
-        <v>176973</v>
+        <v>175064</v>
       </c>
       <c r="D226" t="n">
-        <v>173544</v>
+        <v>172686</v>
       </c>
       <c r="E226" t="n">
-        <v>176973</v>
+        <v>175064</v>
       </c>
       <c r="F226" t="n">
-        <v>9086100</v>
+        <v>15551600</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="B227" t="n">
-        <v>177356</v>
+        <v>172198</v>
       </c>
       <c r="C227" t="n">
-        <v>178199</v>
+        <v>173975</v>
       </c>
       <c r="D227" t="n">
-        <v>174279</v>
+        <v>171793</v>
       </c>
       <c r="E227" t="n">
-        <v>174279</v>
+        <v>173790</v>
       </c>
       <c r="F227" t="n">
-        <v>9365700</v>
+        <v>9892300</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46163</v>
+        <v>46175</v>
       </c>
       <c r="B228" t="n">
-        <v>177650</v>
+        <v>174198</v>
       </c>
       <c r="C228" t="n">
-        <v>178547</v>
+        <v>174894</v>
       </c>
       <c r="D228" t="n">
-        <v>175805</v>
+        <v>172199</v>
       </c>
       <c r="E228" t="n">
-        <v>177352</v>
+        <v>172199</v>
       </c>
       <c r="F228" t="n">
-        <v>7354500</v>
+        <v>7503900</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46164</v>
+        <v>46176</v>
       </c>
       <c r="B229" t="n">
-        <v>176210</v>
+        <v>170331</v>
       </c>
       <c r="C229" t="n">
-        <v>177649</v>
+        <v>174192</v>
       </c>
       <c r="D229" t="n">
-        <v>174893</v>
+        <v>170008</v>
       </c>
       <c r="E229" t="n">
-        <v>177649</v>
+        <v>174192</v>
       </c>
       <c r="F229" t="n">
-        <v>6760900</v>
+        <v>9974200</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46167</v>
+        <v>46178</v>
       </c>
       <c r="B230" t="n">
-        <v>177359</v>
+        <v>169019</v>
       </c>
       <c r="C230" t="n">
-        <v>177512</v>
+        <v>170457</v>
       </c>
       <c r="D230" t="n">
-        <v>176210</v>
+        <v>168910</v>
       </c>
       <c r="E230" t="n">
-        <v>176210</v>
+        <v>170331</v>
       </c>
       <c r="F230" t="n">
-        <v>2377600</v>
+        <v>8585100</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46168</v>
+        <v>46181</v>
       </c>
       <c r="B231" t="n">
-        <v>176589</v>
+        <v>168669</v>
       </c>
       <c r="C231" t="n">
-        <v>177816</v>
+        <v>169646</v>
       </c>
       <c r="D231" t="n">
-        <v>175516</v>
+        <v>168130</v>
       </c>
       <c r="E231" t="n">
-        <v>177816</v>
+        <v>169042</v>
       </c>
       <c r="F231" t="n">
-        <v>7402600</v>
+        <v>7438000</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="B232" t="n">
-        <v>175744</v>
+        <v>169813</v>
       </c>
       <c r="C232" t="n">
-        <v>177640</v>
+        <v>170601</v>
       </c>
       <c r="D232" t="n">
-        <v>175555</v>
+        <v>168406</v>
       </c>
       <c r="E232" t="n">
-        <v>176602</v>
+        <v>168673</v>
       </c>
       <c r="F232" t="n">
-        <v>7310400</v>
+        <v>8440200</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="B233" t="n">
-        <v>175063</v>
+        <v>168619</v>
       </c>
       <c r="C233" t="n">
-        <v>176627</v>
+        <v>169813</v>
       </c>
       <c r="D233" t="n">
-        <v>174686</v>
+        <v>168071</v>
       </c>
       <c r="E233" t="n">
-        <v>175744</v>
+        <v>169813</v>
       </c>
       <c r="F233" t="n">
-        <v>7376200</v>
+        <v>8732300</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46171</v>
+        <v>46184</v>
       </c>
       <c r="B234" t="n">
-        <v>173788</v>
+        <v>171497</v>
       </c>
       <c r="C234" t="n">
-        <v>175064</v>
+        <v>171927</v>
       </c>
       <c r="D234" t="n">
-        <v>172686</v>
+        <v>168280</v>
       </c>
       <c r="E234" t="n">
-        <v>175064</v>
+        <v>168619</v>
       </c>
       <c r="F234" t="n">
-        <v>15551600</v>
+        <v>10576900</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="B235" t="n">
-        <v>172198</v>
+        <v>171133</v>
       </c>
       <c r="C235" t="n">
-        <v>173975</v>
+        <v>172545</v>
       </c>
       <c r="D235" t="n">
-        <v>171793</v>
+        <v>169993</v>
       </c>
       <c r="E235" t="n">
-        <v>173790</v>
+        <v>171497</v>
       </c>
       <c r="F235" t="n">
-        <v>9892300</v>
+        <v>7013700</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46175</v>
+        <v>46188</v>
       </c>
       <c r="B236" t="n">
-        <v>174198</v>
+        <v>170415</v>
       </c>
       <c r="C236" t="n">
-        <v>174894</v>
+        <v>174228</v>
       </c>
       <c r="D236" t="n">
-        <v>172199</v>
+        <v>170351</v>
       </c>
       <c r="E236" t="n">
-        <v>172199</v>
+        <v>171139</v>
       </c>
       <c r="F236" t="n">
-        <v>7503900</v>
+        <v>8709200</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46176</v>
+        <v>46189</v>
       </c>
       <c r="B237" t="n">
-        <v>170331</v>
+        <v>169649</v>
       </c>
       <c r="C237" t="n">
-        <v>174192</v>
+        <v>170416</v>
       </c>
       <c r="D237" t="n">
-        <v>170008</v>
+        <v>169121</v>
       </c>
       <c r="E237" t="n">
-        <v>174192</v>
+        <v>170416</v>
       </c>
       <c r="F237" t="n">
-        <v>9974200</v>
+        <v>8765700</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46178</v>
+        <v>46190</v>
       </c>
       <c r="B238" t="n">
-        <v>169019</v>
+        <v>168454</v>
       </c>
       <c r="C238" t="n">
-        <v>170457</v>
+        <v>171878</v>
       </c>
       <c r="D238" t="n">
-        <v>168910</v>
+        <v>167916</v>
       </c>
       <c r="E238" t="n">
-        <v>170331</v>
+        <v>169649</v>
       </c>
       <c r="F238" t="n">
-        <v>8585100</v>
+        <v>10732100</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46181</v>
+        <v>46191</v>
       </c>
       <c r="B239" t="n">
-        <v>168669</v>
+        <v>168278</v>
       </c>
       <c r="C239" t="n">
-        <v>169646</v>
+        <v>169542</v>
       </c>
       <c r="D239" t="n">
-        <v>168130</v>
+        <v>167911</v>
       </c>
       <c r="E239" t="n">
-        <v>169042</v>
+        <v>168467</v>
       </c>
       <c r="F239" t="n">
-        <v>7438000</v>
+        <v>9236700</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46182</v>
+        <v>46192</v>
       </c>
       <c r="B240" t="n">
-        <v>169813</v>
+        <v>168576</v>
       </c>
       <c r="C240" t="n">
-        <v>170601</v>
+        <v>168787</v>
       </c>
       <c r="D240" t="n">
-        <v>168406</v>
+        <v>167658</v>
       </c>
       <c r="E240" t="n">
-        <v>168673</v>
+        <v>168279</v>
       </c>
       <c r="F240" t="n">
-        <v>8440200</v>
+        <v>4847900</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="B241" t="n">
-        <v>168619</v>
+        <v>170370</v>
       </c>
       <c r="C241" t="n">
-        <v>169813</v>
+        <v>170750</v>
       </c>
       <c r="D241" t="n">
-        <v>168071</v>
+        <v>168326</v>
       </c>
       <c r="E241" t="n">
-        <v>169813</v>
+        <v>168334</v>
       </c>
       <c r="F241" t="n">
-        <v>8732300</v>
+        <v>8544200</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="B242" t="n">
-        <v>171497</v>
+        <v>171259</v>
       </c>
       <c r="C242" t="n">
-        <v>171927</v>
+        <v>171720</v>
       </c>
       <c r="D242" t="n">
-        <v>168280</v>
+        <v>168495</v>
       </c>
       <c r="E242" t="n">
-        <v>168619</v>
+        <v>170367</v>
       </c>
       <c r="F242" t="n">
-        <v>10576900</v>
+        <v>7598800</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="B243" t="n">
-        <v>171133</v>
+        <v>170507</v>
       </c>
       <c r="C243" t="n">
-        <v>172545</v>
+        <v>171342</v>
       </c>
       <c r="D243" t="n">
-        <v>169993</v>
+        <v>169668</v>
       </c>
       <c r="E243" t="n">
-        <v>171497</v>
+        <v>171256</v>
       </c>
       <c r="F243" t="n">
-        <v>7013700</v>
+        <v>9571200</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46188</v>
+        <v>46198</v>
       </c>
       <c r="B244" t="n">
-        <v>170415</v>
+        <v>171990</v>
       </c>
       <c r="C244" t="n">
-        <v>174228</v>
+        <v>173277</v>
       </c>
       <c r="D244" t="n">
-        <v>170351</v>
+        <v>170508</v>
       </c>
       <c r="E244" t="n">
-        <v>171139</v>
+        <v>170508</v>
       </c>
       <c r="F244" t="n">
-        <v>8709200</v>
+        <v>7620600</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="B245" t="n">
-        <v>169649</v>
+        <v>173295</v>
       </c>
       <c r="C245" t="n">
-        <v>170416</v>
+        <v>173964</v>
       </c>
       <c r="D245" t="n">
-        <v>169121</v>
+        <v>171124</v>
       </c>
       <c r="E245" t="n">
-        <v>170416</v>
+        <v>171990</v>
       </c>
       <c r="F245" t="n">
-        <v>8765700</v>
+        <v>6921000</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46190</v>
+        <v>46202</v>
       </c>
       <c r="B246" t="n">
-        <v>168454</v>
+        <v>173205</v>
       </c>
       <c r="C246" t="n">
-        <v>171878</v>
+        <v>173892</v>
       </c>
       <c r="D246" t="n">
-        <v>167916</v>
+        <v>172393</v>
       </c>
       <c r="E246" t="n">
-        <v>169649</v>
+        <v>173294</v>
       </c>
       <c r="F246" t="n">
-        <v>10732100</v>
+        <v>4909900</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46191</v>
+        <v>46203</v>
       </c>
       <c r="B247" t="n">
-        <v>168278</v>
+        <v>172024</v>
       </c>
       <c r="C247" t="n">
-        <v>169542</v>
+        <v>173205</v>
       </c>
       <c r="D247" t="n">
-        <v>167911</v>
+        <v>170539</v>
       </c>
       <c r="E247" t="n">
-        <v>168467</v>
+        <v>173205</v>
       </c>
       <c r="F247" t="n">
-        <v>9236700</v>
+        <v>7692000</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46192</v>
+        <v>46204</v>
       </c>
       <c r="B248" t="n">
-        <v>168576</v>
+        <v>171689</v>
       </c>
       <c r="C248" t="n">
-        <v>168787</v>
+        <v>172098</v>
       </c>
       <c r="D248" t="n">
-        <v>167658</v>
+        <v>169666</v>
       </c>
       <c r="E248" t="n">
-        <v>168279</v>
+        <v>172017</v>
       </c>
       <c r="F248" t="n">
-        <v>4847900</v>
+        <v>7659700</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="B249" t="n">
-        <v>170370</v>
+        <v>172788</v>
       </c>
       <c r="C249" t="n">
-        <v>170750</v>
+        <v>174426</v>
       </c>
       <c r="D249" t="n">
-        <v>168326</v>
+        <v>171697</v>
       </c>
       <c r="E249" t="n">
-        <v>168334</v>
+        <v>171698</v>
       </c>
       <c r="F249" t="n">
-        <v>8544200</v>
+        <v>6513500</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46196</v>
+        <v>46206</v>
       </c>
       <c r="B250" t="n">
-        <v>171259</v>
+        <v>174266</v>
       </c>
       <c r="C250" t="n">
-        <v>171720</v>
+        <v>174664</v>
       </c>
       <c r="D250" t="n">
-        <v>168495</v>
+        <v>172790</v>
       </c>
       <c r="E250" t="n">
-        <v>170367</v>
+        <v>172790</v>
       </c>
       <c r="F250" t="n">
-        <v>7598800</v>
+        <v>2949700</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46197</v>
+        <v>46209</v>
       </c>
       <c r="B251" t="n">
-        <v>170507</v>
+        <v>172447.578125</v>
       </c>
       <c r="C251" t="n">
-        <v>171342</v>
+        <v>174057.46875</v>
       </c>
       <c r="D251" t="n">
-        <v>169668</v>
+        <v>171621.703125</v>
       </c>
       <c r="E251" t="n">
-        <v>171256</v>
+        <v>174057.46875</v>
       </c>
       <c r="F251" t="n">
-        <v>9571200</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
-        <v>46198</v>
-      </c>
-      <c r="B252" t="n">
-        <v>172027.875</v>
-      </c>
-      <c r="C252" t="n">
-        <v>173277.09375</v>
-      </c>
-      <c r="D252" t="n">
-        <v>170507.921875</v>
-      </c>
-      <c r="E252" t="n">
-        <v>170507.921875</v>
-      </c>
-      <c r="F252" t="n">
         <v>0</v>
       </c>
     </row>
